--- a/__履歴__/s4_002_isolated_node_filtering_all199.xlsx
+++ b/__履歴__/s4_002_isolated_node_filtering_all199.xlsx
@@ -476,22 +476,22 @@
         <v>34247</v>
       </c>
       <c r="D2" t="n">
-        <v>29794</v>
+        <v>32644</v>
       </c>
       <c r="E2" t="n">
-        <v>4453</v>
+        <v>1603</v>
       </c>
       <c r="F2" t="n">
-        <v>13.00259876777528</v>
+        <v>4.680701959295705</v>
       </c>
       <c r="G2" t="n">
         <v>1.329722384003106</v>
       </c>
       <c r="H2" t="n">
-        <v>1.156823917685886</v>
+        <v>1.267482042321879</v>
       </c>
       <c r="I2" t="n">
-        <v>22527</v>
+        <v>27254</v>
       </c>
     </row>
     <row r="3">
@@ -507,22 +507,22 @@
         <v>39552</v>
       </c>
       <c r="D3" t="n">
-        <v>32123</v>
+        <v>35840</v>
       </c>
       <c r="E3" t="n">
-        <v>7429</v>
+        <v>3712</v>
       </c>
       <c r="F3" t="n">
-        <v>18.78286812297735</v>
+        <v>9.385113268608414</v>
       </c>
       <c r="G3" t="n">
         <v>1.206037505717335</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9795090715048026</v>
+        <v>1.092849519743863</v>
       </c>
       <c r="I3" t="n">
-        <v>23938</v>
+        <v>29085</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         <v>32643</v>
       </c>
       <c r="D4" t="n">
-        <v>27772</v>
+        <v>30835</v>
       </c>
       <c r="E4" t="n">
-        <v>4871</v>
+        <v>1808</v>
       </c>
       <c r="F4" t="n">
-        <v>14.92203535214288</v>
+        <v>5.538706613975431</v>
       </c>
       <c r="G4" t="n">
         <v>1.167572787753058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9933471636025467</v>
+        <v>1.102904356534802</v>
       </c>
       <c r="I4" t="n">
-        <v>21197</v>
+        <v>26249</v>
       </c>
     </row>
     <row r="5">
@@ -569,22 +569,22 @@
         <v>18757</v>
       </c>
       <c r="D5" t="n">
-        <v>14811</v>
+        <v>17711</v>
       </c>
       <c r="E5" t="n">
-        <v>3946</v>
+        <v>1046</v>
       </c>
       <c r="F5" t="n">
-        <v>21.03747934104601</v>
+        <v>5.576584741696433</v>
       </c>
       <c r="G5" t="n">
         <v>1.223149657645908</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9658298011085752</v>
+        <v>1.154939680469514</v>
       </c>
       <c r="I5" t="n">
-        <v>11293</v>
+        <v>15081</v>
       </c>
     </row>
     <row r="6">
@@ -600,22 +600,22 @@
         <v>71790</v>
       </c>
       <c r="D6" t="n">
-        <v>66211</v>
+        <v>68646</v>
       </c>
       <c r="E6" t="n">
-        <v>5579</v>
+        <v>3144</v>
       </c>
       <c r="F6" t="n">
-        <v>7.771277336676417</v>
+        <v>4.37944003343084</v>
       </c>
       <c r="G6" t="n">
         <v>1.223581947095719</v>
       </c>
       <c r="H6" t="n">
-        <v>1.128494000545405</v>
+        <v>1.169995909462776</v>
       </c>
       <c r="I6" t="n">
-        <v>55300</v>
+        <v>60792</v>
       </c>
     </row>
     <row r="7">
@@ -631,22 +631,22 @@
         <v>79534</v>
       </c>
       <c r="D7" t="n">
-        <v>74301</v>
+        <v>76128</v>
       </c>
       <c r="E7" t="n">
-        <v>5233</v>
+        <v>3406</v>
       </c>
       <c r="F7" t="n">
-        <v>6.579576030376947</v>
+        <v>4.282445243543641</v>
       </c>
       <c r="G7" t="n">
         <v>1.216562652961331</v>
       </c>
       <c r="H7" t="n">
-        <v>1.13651798825257</v>
+        <v>1.16446402349486</v>
       </c>
       <c r="I7" t="n">
-        <v>64876</v>
+        <v>68214</v>
       </c>
     </row>
     <row r="8">
@@ -662,22 +662,22 @@
         <v>20551</v>
       </c>
       <c r="D8" t="n">
-        <v>18871</v>
+        <v>19562</v>
       </c>
       <c r="E8" t="n">
-        <v>1680</v>
+        <v>989</v>
       </c>
       <c r="F8" t="n">
-        <v>8.174784682010609</v>
+        <v>4.812417887207435</v>
       </c>
       <c r="G8" t="n">
         <v>1.162584148894043</v>
       </c>
       <c r="H8" t="n">
-        <v>1.06754539797477</v>
+        <v>1.106635741358828</v>
       </c>
       <c r="I8" t="n">
-        <v>15667</v>
+        <v>16989</v>
       </c>
     </row>
     <row r="9">
@@ -693,22 +693,22 @@
         <v>94321</v>
       </c>
       <c r="D9" t="n">
-        <v>79789</v>
+        <v>88471</v>
       </c>
       <c r="E9" t="n">
-        <v>14532</v>
+        <v>5850</v>
       </c>
       <c r="F9" t="n">
-        <v>15.40696133416736</v>
+        <v>6.202224319080586</v>
       </c>
       <c r="G9" t="n">
         <v>1.199341335639083</v>
       </c>
       <c r="H9" t="n">
-        <v>1.014559279792483</v>
+        <v>1.124955495651289</v>
       </c>
       <c r="I9" t="n">
-        <v>59833</v>
+        <v>74022</v>
       </c>
     </row>
     <row r="10">
@@ -724,22 +724,22 @@
         <v>40754</v>
       </c>
       <c r="D10" t="n">
-        <v>35973</v>
+        <v>38508</v>
       </c>
       <c r="E10" t="n">
-        <v>4781</v>
+        <v>2246</v>
       </c>
       <c r="F10" t="n">
-        <v>11.73136379251117</v>
+        <v>5.511115473327771</v>
       </c>
       <c r="G10" t="n">
         <v>1.137585484996511</v>
       </c>
       <c r="H10" t="n">
-        <v>1.004131193300768</v>
+        <v>1.074891835310537</v>
       </c>
       <c r="I10" t="n">
-        <v>28537</v>
+        <v>33146</v>
       </c>
     </row>
     <row r="11">
@@ -755,22 +755,22 @@
         <v>30320</v>
       </c>
       <c r="D11" t="n">
-        <v>24987</v>
+        <v>28831</v>
       </c>
       <c r="E11" t="n">
-        <v>5333</v>
+        <v>1489</v>
       </c>
       <c r="F11" t="n">
-        <v>17.58905013192612</v>
+        <v>4.910949868073879</v>
       </c>
       <c r="G11" t="n">
         <v>1.15053314613137</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9481652942738967</v>
+        <v>1.094031040109285</v>
       </c>
       <c r="I11" t="n">
-        <v>18566</v>
+        <v>24653</v>
       </c>
     </row>
     <row r="12">
@@ -786,22 +786,22 @@
         <v>24129</v>
       </c>
       <c r="D12" t="n">
-        <v>17495</v>
+        <v>22304</v>
       </c>
       <c r="E12" t="n">
-        <v>6634</v>
+        <v>1825</v>
       </c>
       <c r="F12" t="n">
-        <v>27.49388702391313</v>
+        <v>7.5635127854449</v>
       </c>
       <c r="G12" t="n">
         <v>1.26131730266597</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9145321484579195</v>
+        <v>1.1659174072138</v>
       </c>
       <c r="I12" t="n">
-        <v>12501</v>
+        <v>18440</v>
       </c>
     </row>
     <row r="13">
@@ -817,22 +817,22 @@
         <v>61224</v>
       </c>
       <c r="D13" t="n">
-        <v>55526</v>
+        <v>58034</v>
       </c>
       <c r="E13" t="n">
-        <v>5698</v>
+        <v>3190</v>
       </c>
       <c r="F13" t="n">
-        <v>9.306807787795636</v>
+        <v>5.210375016333464</v>
       </c>
       <c r="G13" t="n">
         <v>1.086167438394805</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9850799226497774</v>
+        <v>1.029574041549133</v>
       </c>
       <c r="I13" t="n">
-        <v>45373</v>
+        <v>50004</v>
       </c>
     </row>
     <row r="14">
@@ -848,22 +848,22 @@
         <v>28127</v>
       </c>
       <c r="D14" t="n">
-        <v>21663</v>
+        <v>25426</v>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>2701</v>
       </c>
       <c r="F14" t="n">
-        <v>22.98147687275572</v>
+        <v>9.602872684609094</v>
       </c>
       <c r="G14" t="n">
         <v>1.154259684832567</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8889937623112278</v>
+        <v>1.043417596848326</v>
       </c>
       <c r="I14" t="n">
-        <v>15589</v>
+        <v>20341</v>
       </c>
     </row>
     <row r="15">
@@ -879,22 +879,22 @@
         <v>26348</v>
       </c>
       <c r="D15" t="n">
-        <v>20419</v>
+        <v>24475</v>
       </c>
       <c r="E15" t="n">
-        <v>5929</v>
+        <v>1873</v>
       </c>
       <c r="F15" t="n">
-        <v>22.50265674814028</v>
+        <v>7.108698952482162</v>
       </c>
       <c r="G15" t="n">
         <v>1.129361337333905</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8752250321474496</v>
+        <v>1.049078439777111</v>
       </c>
       <c r="I15" t="n">
-        <v>14793</v>
+        <v>20537</v>
       </c>
     </row>
     <row r="16">
@@ -910,22 +910,22 @@
         <v>9006</v>
       </c>
       <c r="D16" t="n">
-        <v>8510</v>
+        <v>8691</v>
       </c>
       <c r="E16" t="n">
-        <v>496</v>
+        <v>315</v>
       </c>
       <c r="F16" t="n">
-        <v>5.507439484787919</v>
+        <v>3.497668221185876</v>
       </c>
       <c r="G16" t="n">
         <v>1.211135018827326</v>
       </c>
       <c r="H16" t="n">
-        <v>1.144432490586337</v>
+        <v>1.16877353415815</v>
       </c>
       <c r="I16" t="n">
-        <v>7270</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="17">
@@ -941,22 +941,22 @@
         <v>49887</v>
       </c>
       <c r="D17" t="n">
-        <v>44342</v>
+        <v>47334</v>
       </c>
       <c r="E17" t="n">
-        <v>5545</v>
+        <v>2553</v>
       </c>
       <c r="F17" t="n">
-        <v>11.11512017158779</v>
+        <v>5.117565698478561</v>
       </c>
       <c r="G17" t="n">
         <v>1.230380308785084</v>
       </c>
       <c r="H17" t="n">
-        <v>1.093622058896069</v>
+        <v>1.167414788141864</v>
       </c>
       <c r="I17" t="n">
-        <v>35500</v>
+        <v>41004</v>
       </c>
     </row>
     <row r="18">
@@ -972,22 +972,22 @@
         <v>39219</v>
       </c>
       <c r="D18" t="n">
-        <v>35039</v>
+        <v>36871</v>
       </c>
       <c r="E18" t="n">
-        <v>4180</v>
+        <v>2348</v>
       </c>
       <c r="F18" t="n">
-        <v>10.65809939060149</v>
+        <v>5.986894107447921</v>
       </c>
       <c r="G18" t="n">
         <v>1.228011397438707</v>
       </c>
       <c r="H18" t="n">
-        <v>1.097128722171776</v>
+        <v>1.154491655446661</v>
       </c>
       <c r="I18" t="n">
-        <v>28381</v>
+        <v>31751</v>
       </c>
     </row>
     <row r="19">
@@ -1003,22 +1003,22 @@
         <v>40358</v>
       </c>
       <c r="D19" t="n">
-        <v>36103</v>
+        <v>38081</v>
       </c>
       <c r="E19" t="n">
-        <v>4255</v>
+        <v>2277</v>
       </c>
       <c r="F19" t="n">
-        <v>10.54313890678428</v>
+        <v>5.642004063630507</v>
       </c>
       <c r="G19" t="n">
         <v>1.234907132584682</v>
       </c>
       <c r="H19" t="n">
-        <v>1.104709158226493</v>
+        <v>1.165233621982191</v>
       </c>
       <c r="I19" t="n">
-        <v>29110</v>
+        <v>32900</v>
       </c>
     </row>
     <row r="20">
@@ -1034,22 +1034,22 @@
         <v>60127</v>
       </c>
       <c r="D20" t="n">
-        <v>56049</v>
+        <v>57593</v>
       </c>
       <c r="E20" t="n">
-        <v>4078</v>
+        <v>2534</v>
       </c>
       <c r="F20" t="n">
-        <v>6.782310775525138</v>
+        <v>4.214412826184576</v>
       </c>
       <c r="G20" t="n">
         <v>1.049483348460518</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9783041262305383</v>
+        <v>1.005253787614327</v>
       </c>
       <c r="I20" t="n">
-        <v>47833</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="21">
@@ -1065,22 +1065,22 @@
         <v>45945</v>
       </c>
       <c r="D21" t="n">
-        <v>41120</v>
+        <v>43300</v>
       </c>
       <c r="E21" t="n">
-        <v>4825</v>
+        <v>2645</v>
       </c>
       <c r="F21" t="n">
-        <v>10.50168679943411</v>
+        <v>5.756883229948852</v>
       </c>
       <c r="G21" t="n">
         <v>1.186749321968229</v>
       </c>
       <c r="H21" t="n">
-        <v>1.062120625080718</v>
+        <v>1.118429549270309</v>
       </c>
       <c r="I21" t="n">
-        <v>32977</v>
+        <v>37119</v>
       </c>
     </row>
     <row r="22">
@@ -1096,22 +1096,22 @@
         <v>73498</v>
       </c>
       <c r="D22" t="n">
-        <v>66256</v>
+        <v>69379</v>
       </c>
       <c r="E22" t="n">
-        <v>7242</v>
+        <v>4119</v>
       </c>
       <c r="F22" t="n">
-        <v>9.853329342295028</v>
+        <v>5.604234128819831</v>
       </c>
       <c r="G22" t="n">
         <v>1.275409096430493</v>
       </c>
       <c r="H22" t="n">
-        <v>1.149738837697607</v>
+        <v>1.203932184566262</v>
       </c>
       <c r="I22" t="n">
-        <v>54448</v>
+        <v>60126</v>
       </c>
     </row>
     <row r="23">
@@ -1127,22 +1127,22 @@
         <v>20528</v>
       </c>
       <c r="D23" t="n">
-        <v>18054</v>
+        <v>19033</v>
       </c>
       <c r="E23" t="n">
-        <v>2474</v>
+        <v>1495</v>
       </c>
       <c r="F23" t="n">
-        <v>12.05183164458301</v>
+        <v>7.282735775526112</v>
       </c>
       <c r="G23" t="n">
         <v>1.04044602128738</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9150532184490623</v>
+        <v>0.9646730866700456</v>
       </c>
       <c r="I23" t="n">
-        <v>14541</v>
+        <v>16113</v>
       </c>
     </row>
     <row r="24">
@@ -1158,22 +1158,22 @@
         <v>20871</v>
       </c>
       <c r="D24" t="n">
-        <v>17468</v>
+        <v>19927</v>
       </c>
       <c r="E24" t="n">
-        <v>3403</v>
+        <v>944</v>
       </c>
       <c r="F24" t="n">
-        <v>16.30492070336831</v>
+        <v>4.523022375545015</v>
       </c>
       <c r="G24" t="n">
         <v>1.150741577989745</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9631140761978276</v>
+        <v>1.098693278932569</v>
       </c>
       <c r="I24" t="n">
-        <v>13498</v>
+        <v>17037</v>
       </c>
     </row>
     <row r="25">
@@ -1189,22 +1189,22 @@
         <v>38432</v>
       </c>
       <c r="D25" t="n">
-        <v>33722</v>
+        <v>35778</v>
       </c>
       <c r="E25" t="n">
-        <v>4710</v>
+        <v>2654</v>
       </c>
       <c r="F25" t="n">
-        <v>12.25541215653622</v>
+        <v>6.905703580349709</v>
       </c>
       <c r="G25" t="n">
         <v>1.301941122666757</v>
       </c>
       <c r="H25" t="n">
-        <v>1.142382872048511</v>
+        <v>1.212032927944714</v>
       </c>
       <c r="I25" t="n">
-        <v>27037</v>
+        <v>30466</v>
       </c>
     </row>
     <row r="26">
@@ -1220,22 +1220,22 @@
         <v>41494</v>
       </c>
       <c r="D26" t="n">
-        <v>37017</v>
+        <v>39651</v>
       </c>
       <c r="E26" t="n">
-        <v>4477</v>
+        <v>1843</v>
       </c>
       <c r="F26" t="n">
-        <v>10.78951173663662</v>
+        <v>4.441606015327517</v>
       </c>
       <c r="G26" t="n">
         <v>1.045162590362963</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9323946500088159</v>
+        <v>0.9987405858794489</v>
       </c>
       <c r="I26" t="n">
-        <v>29432</v>
+        <v>34432</v>
       </c>
     </row>
     <row r="27">
@@ -1251,22 +1251,22 @@
         <v>60061</v>
       </c>
       <c r="D27" t="n">
-        <v>55844</v>
+        <v>57263</v>
       </c>
       <c r="E27" t="n">
-        <v>4217</v>
+        <v>2798</v>
       </c>
       <c r="F27" t="n">
-        <v>7.021195118296399</v>
+        <v>4.658597092955495</v>
       </c>
       <c r="G27" t="n">
         <v>1.139461202807816</v>
       </c>
       <c r="H27" t="n">
-        <v>1.059457408461393</v>
+        <v>1.086378296338456</v>
       </c>
       <c r="I27" t="n">
-        <v>48054</v>
+        <v>50867</v>
       </c>
     </row>
     <row r="28">
@@ -1282,22 +1282,22 @@
         <v>90119</v>
       </c>
       <c r="D28" t="n">
-        <v>82663</v>
+        <v>85585</v>
       </c>
       <c r="E28" t="n">
-        <v>7456</v>
+        <v>4534</v>
       </c>
       <c r="F28" t="n">
-        <v>8.273505032235155</v>
+        <v>5.031125511823256</v>
       </c>
       <c r="G28" t="n">
         <v>1.28929296975593</v>
       </c>
       <c r="H28" t="n">
-        <v>1.182623251022919</v>
+        <v>1.224427022232396</v>
       </c>
       <c r="I28" t="n">
-        <v>70380</v>
+        <v>75833</v>
       </c>
     </row>
     <row r="29">
@@ -1313,22 +1313,22 @@
         <v>83663</v>
       </c>
       <c r="D29" t="n">
-        <v>76640</v>
+        <v>79442</v>
       </c>
       <c r="E29" t="n">
-        <v>7023</v>
+        <v>4221</v>
       </c>
       <c r="F29" t="n">
-        <v>8.394391786094211</v>
+        <v>5.045241026499169</v>
       </c>
       <c r="G29" t="n">
         <v>1.236009336957806</v>
       </c>
       <c r="H29" t="n">
-        <v>1.132253870700863</v>
+        <v>1.173649686798251</v>
       </c>
       <c r="I29" t="n">
-        <v>64943</v>
+        <v>70142</v>
       </c>
     </row>
     <row r="30">
@@ -1344,22 +1344,22 @@
         <v>16787</v>
       </c>
       <c r="D30" t="n">
-        <v>14862</v>
+        <v>15545</v>
       </c>
       <c r="E30" t="n">
-        <v>1925</v>
+        <v>1242</v>
       </c>
       <c r="F30" t="n">
-        <v>11.46720676714124</v>
+        <v>7.398582236254245</v>
       </c>
       <c r="G30" t="n">
         <v>1.11245858184228</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9848906560636183</v>
+        <v>1.030152418820411</v>
       </c>
       <c r="I30" t="n">
-        <v>12093</v>
+        <v>13187</v>
       </c>
     </row>
     <row r="31">
@@ -1375,22 +1375,22 @@
         <v>82392</v>
       </c>
       <c r="D31" t="n">
-        <v>74928</v>
+        <v>77854</v>
       </c>
       <c r="E31" t="n">
-        <v>7464</v>
+        <v>4538</v>
       </c>
       <c r="F31" t="n">
-        <v>9.059131954558696</v>
+        <v>5.507816292843965</v>
       </c>
       <c r="G31" t="n">
         <v>1.232343175087499</v>
       </c>
       <c r="H31" t="n">
-        <v>1.120703580723324</v>
+        <v>1.164467976906279</v>
       </c>
       <c r="I31" t="n">
-        <v>62306</v>
+        <v>67948</v>
       </c>
     </row>
     <row r="32">
@@ -1406,22 +1406,22 @@
         <v>67550</v>
       </c>
       <c r="D32" t="n">
-        <v>63218</v>
+        <v>64894</v>
       </c>
       <c r="E32" t="n">
-        <v>4332</v>
+        <v>2656</v>
       </c>
       <c r="F32" t="n">
-        <v>6.413027387120652</v>
+        <v>3.931902294596595</v>
       </c>
       <c r="G32" t="n">
         <v>1.204958972529433</v>
       </c>
       <c r="H32" t="n">
-        <v>1.127684623617553</v>
+        <v>1.1575811630396</v>
       </c>
       <c r="I32" t="n">
-        <v>53978</v>
+        <v>58103</v>
       </c>
     </row>
     <row r="33">
@@ -1437,22 +1437,22 @@
         <v>18296</v>
       </c>
       <c r="D33" t="n">
-        <v>17369</v>
+        <v>17681</v>
       </c>
       <c r="E33" t="n">
-        <v>927</v>
+        <v>615</v>
       </c>
       <c r="F33" t="n">
-        <v>5.066681241801486</v>
+        <v>3.361390467861828</v>
       </c>
       <c r="G33" t="n">
         <v>1.16224113835599</v>
       </c>
       <c r="H33" t="n">
-        <v>1.103354084614407</v>
+        <v>1.123173675517723</v>
       </c>
       <c r="I33" t="n">
-        <v>15257</v>
+        <v>16014</v>
       </c>
     </row>
     <row r="34">
@@ -1468,22 +1468,22 @@
         <v>12215</v>
       </c>
       <c r="D34" t="n">
-        <v>11611</v>
+        <v>11804</v>
       </c>
       <c r="E34" t="n">
-        <v>604</v>
+        <v>411</v>
       </c>
       <c r="F34" t="n">
-        <v>4.944740073679902</v>
+        <v>3.364715513712648</v>
       </c>
       <c r="G34" t="n">
         <v>1.215181058495822</v>
       </c>
       <c r="H34" t="n">
-        <v>1.155093513728611</v>
+        <v>1.174293672900915</v>
       </c>
       <c r="I34" t="n">
-        <v>10170</v>
+        <v>10708</v>
       </c>
     </row>
     <row r="35">
@@ -1499,22 +1499,22 @@
         <v>31999</v>
       </c>
       <c r="D35" t="n">
-        <v>24538</v>
+        <v>29117</v>
       </c>
       <c r="E35" t="n">
-        <v>7461</v>
+        <v>2882</v>
       </c>
       <c r="F35" t="n">
-        <v>23.31635363605113</v>
+        <v>9.006531454107941</v>
       </c>
       <c r="G35" t="n">
         <v>1.138673404028183</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8731762863853106</v>
+        <v>1.036118425734823</v>
       </c>
       <c r="I35" t="n">
-        <v>17668</v>
+        <v>23486</v>
       </c>
     </row>
     <row r="36">
@@ -1530,22 +1530,22 @@
         <v>39519</v>
       </c>
       <c r="D36" t="n">
-        <v>35203</v>
+        <v>37024</v>
       </c>
       <c r="E36" t="n">
-        <v>4316</v>
+        <v>2495</v>
       </c>
       <c r="F36" t="n">
-        <v>10.92132898099648</v>
+        <v>6.313418861813306</v>
       </c>
       <c r="G36" t="n">
         <v>1.228366281238344</v>
       </c>
       <c r="H36" t="n">
-        <v>1.094212358572672</v>
+        <v>1.150814372746488</v>
       </c>
       <c r="I36" t="n">
-        <v>28177</v>
+        <v>31609</v>
       </c>
     </row>
     <row r="37">
@@ -1561,22 +1561,22 @@
         <v>30501</v>
       </c>
       <c r="D37" t="n">
-        <v>28029</v>
+        <v>29105</v>
       </c>
       <c r="E37" t="n">
-        <v>2472</v>
+        <v>1396</v>
       </c>
       <c r="F37" t="n">
-        <v>8.104652306481755</v>
+        <v>4.576899118061703</v>
       </c>
       <c r="G37" t="n">
         <v>1.106271081933916</v>
       </c>
       <c r="H37" t="n">
-        <v>1.016611657176018</v>
+        <v>1.055638170541511</v>
       </c>
       <c r="I37" t="n">
-        <v>23279</v>
+        <v>25441</v>
       </c>
     </row>
     <row r="38">
@@ -1592,22 +1592,22 @@
         <v>88252</v>
       </c>
       <c r="D38" t="n">
-        <v>82219</v>
+        <v>84498</v>
       </c>
       <c r="E38" t="n">
-        <v>6033</v>
+        <v>3754</v>
       </c>
       <c r="F38" t="n">
-        <v>6.836105697321307</v>
+        <v>4.253727960839415</v>
       </c>
       <c r="G38" t="n">
         <v>1.179319284272981</v>
       </c>
       <c r="H38" t="n">
-        <v>1.098699771491187</v>
+        <v>1.12915425013029</v>
       </c>
       <c r="I38" t="n">
-        <v>70855</v>
+        <v>75577</v>
       </c>
     </row>
     <row r="39">
@@ -1623,22 +1623,22 @@
         <v>28375</v>
       </c>
       <c r="D39" t="n">
-        <v>23307</v>
+        <v>26746</v>
       </c>
       <c r="E39" t="n">
-        <v>5068</v>
+        <v>1629</v>
       </c>
       <c r="F39" t="n">
-        <v>17.86079295154185</v>
+        <v>5.740969162995595</v>
       </c>
       <c r="G39" t="n">
         <v>1.111350462165126</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9128544571518095</v>
+        <v>1.047548174839417</v>
       </c>
       <c r="I39" t="n">
-        <v>17146</v>
+        <v>22628</v>
       </c>
     </row>
     <row r="40">
@@ -1654,22 +1654,22 @@
         <v>42883</v>
       </c>
       <c r="D40" t="n">
-        <v>36836</v>
+        <v>40312</v>
       </c>
       <c r="E40" t="n">
-        <v>6047</v>
+        <v>2571</v>
       </c>
       <c r="F40" t="n">
-        <v>14.10115896742299</v>
+        <v>5.995382785719283</v>
       </c>
       <c r="G40" t="n">
         <v>1.153419941364749</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9907743618709487</v>
+        <v>1.084268000753113</v>
       </c>
       <c r="I40" t="n">
-        <v>28368</v>
+        <v>33991</v>
       </c>
     </row>
     <row r="41">
@@ -1685,22 +1685,22 @@
         <v>8717</v>
       </c>
       <c r="D41" t="n">
-        <v>7950</v>
+        <v>8245</v>
       </c>
       <c r="E41" t="n">
-        <v>767</v>
+        <v>472</v>
       </c>
       <c r="F41" t="n">
-        <v>8.798898703682459</v>
+        <v>5.414706894573821</v>
       </c>
       <c r="G41" t="n">
         <v>1.689013757023833</v>
       </c>
       <c r="H41" t="n">
-        <v>1.540399147452044</v>
+        <v>1.597558612671963</v>
       </c>
       <c r="I41" t="n">
-        <v>6708</v>
+        <v>7328</v>
       </c>
     </row>
     <row r="42">
@@ -1716,22 +1716,22 @@
         <v>48562</v>
       </c>
       <c r="D42" t="n">
-        <v>41882</v>
+        <v>45274</v>
       </c>
       <c r="E42" t="n">
-        <v>6680</v>
+        <v>3288</v>
       </c>
       <c r="F42" t="n">
-        <v>13.75561138338619</v>
+        <v>6.770726082121824</v>
       </c>
       <c r="G42" t="n">
         <v>1.357466316319115</v>
       </c>
       <c r="H42" t="n">
-        <v>1.170738525185889</v>
+        <v>1.265555990384078</v>
       </c>
       <c r="I42" t="n">
-        <v>32579</v>
+        <v>38508</v>
       </c>
     </row>
     <row r="43">
@@ -1747,22 +1747,22 @@
         <v>11774</v>
       </c>
       <c r="D43" t="n">
-        <v>11217</v>
+        <v>11388</v>
       </c>
       <c r="E43" t="n">
-        <v>557</v>
+        <v>386</v>
       </c>
       <c r="F43" t="n">
-        <v>4.730762697468999</v>
+        <v>3.278410056055716</v>
       </c>
       <c r="G43" t="n">
         <v>1.554733923148026</v>
       </c>
       <c r="H43" t="n">
-        <v>1.481183150666843</v>
+        <v>1.503763369866632</v>
       </c>
       <c r="I43" t="n">
-        <v>9994</v>
+        <v>10394</v>
       </c>
     </row>
     <row r="44">
@@ -1778,22 +1778,22 @@
         <v>75491</v>
       </c>
       <c r="D44" t="n">
-        <v>68206</v>
+        <v>71174</v>
       </c>
       <c r="E44" t="n">
-        <v>7285</v>
+        <v>4317</v>
       </c>
       <c r="F44" t="n">
-        <v>9.650156972354321</v>
+        <v>5.718562477646342</v>
       </c>
       <c r="G44" t="n">
         <v>1.304335055376056</v>
       </c>
       <c r="H44" t="n">
-        <v>1.178464675086822</v>
+        <v>1.229745840316533</v>
       </c>
       <c r="I44" t="n">
-        <v>56881</v>
+        <v>62135</v>
       </c>
     </row>
     <row r="45">
@@ -1809,22 +1809,22 @@
         <v>76475</v>
       </c>
       <c r="D45" t="n">
-        <v>70948</v>
+        <v>73158</v>
       </c>
       <c r="E45" t="n">
-        <v>5527</v>
+        <v>3317</v>
       </c>
       <c r="F45" t="n">
-        <v>7.227198430859757</v>
+        <v>4.337365152010461</v>
       </c>
       <c r="G45" t="n">
         <v>1.189198855507868</v>
       </c>
       <c r="H45" t="n">
-        <v>1.103253094482802</v>
+        <v>1.137618958760963</v>
       </c>
       <c r="I45" t="n">
-        <v>60856</v>
+        <v>65442</v>
       </c>
     </row>
     <row r="46">
@@ -1840,22 +1840,22 @@
         <v>25855</v>
       </c>
       <c r="D46" t="n">
-        <v>21031</v>
+        <v>24714</v>
       </c>
       <c r="E46" t="n">
-        <v>4824</v>
+        <v>1141</v>
       </c>
       <c r="F46" t="n">
-        <v>18.65789982595243</v>
+        <v>4.413072906594469</v>
       </c>
       <c r="G46" t="n">
         <v>1.122178819444444</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9128038194444444</v>
+        <v>1.07265625</v>
       </c>
       <c r="I46" t="n">
-        <v>15337</v>
+        <v>20990</v>
       </c>
     </row>
     <row r="47">
@@ -1871,22 +1871,22 @@
         <v>77840</v>
       </c>
       <c r="D47" t="n">
-        <v>68248</v>
+        <v>72643</v>
       </c>
       <c r="E47" t="n">
-        <v>9592</v>
+        <v>5197</v>
       </c>
       <c r="F47" t="n">
-        <v>12.32271325796506</v>
+        <v>6.676515930113053</v>
       </c>
       <c r="G47" t="n">
         <v>1.284212957616353</v>
       </c>
       <c r="H47" t="n">
-        <v>1.125963077227657</v>
+        <v>1.198472274924521</v>
       </c>
       <c r="I47" t="n">
-        <v>53911</v>
+        <v>61375</v>
       </c>
     </row>
     <row r="48">
@@ -1902,22 +1902,22 @@
         <v>24464</v>
       </c>
       <c r="D48" t="n">
-        <v>23013</v>
+        <v>23497</v>
       </c>
       <c r="E48" t="n">
-        <v>1451</v>
+        <v>967</v>
       </c>
       <c r="F48" t="n">
-        <v>5.931164159581426</v>
+        <v>3.952746893394375</v>
       </c>
       <c r="G48" t="n">
         <v>1.107018417122947</v>
       </c>
       <c r="H48" t="n">
-        <v>1.041359337526585</v>
+        <v>1.063260781030816</v>
       </c>
       <c r="I48" t="n">
-        <v>20113</v>
+        <v>21013</v>
       </c>
     </row>
     <row r="49">
@@ -1933,22 +1933,22 @@
         <v>30094</v>
       </c>
       <c r="D49" t="n">
-        <v>28079</v>
+        <v>28686</v>
       </c>
       <c r="E49" t="n">
-        <v>2015</v>
+        <v>1408</v>
       </c>
       <c r="F49" t="n">
-        <v>6.695686847876653</v>
+        <v>4.678673489732173</v>
       </c>
       <c r="G49" t="n">
         <v>1.090204318214751</v>
       </c>
       <c r="H49" t="n">
-        <v>1.017207651065063</v>
+        <v>1.039197217794523</v>
       </c>
       <c r="I49" t="n">
-        <v>24053</v>
+        <v>25199</v>
       </c>
     </row>
     <row r="50">
@@ -1964,22 +1964,22 @@
         <v>72766</v>
       </c>
       <c r="D50" t="n">
-        <v>66441</v>
+        <v>69005</v>
       </c>
       <c r="E50" t="n">
-        <v>6325</v>
+        <v>3761</v>
       </c>
       <c r="F50" t="n">
-        <v>8.692246378803286</v>
+        <v>5.168622708407772</v>
       </c>
       <c r="G50" t="n">
         <v>1.218269182474175</v>
       </c>
       <c r="H50" t="n">
-        <v>1.112374223576487</v>
+        <v>1.155301444859281</v>
       </c>
       <c r="I50" t="n">
-        <v>55765</v>
+        <v>60745</v>
       </c>
     </row>
     <row r="51">
@@ -1995,22 +1995,22 @@
         <v>25135</v>
       </c>
       <c r="D51" t="n">
-        <v>17997</v>
+        <v>23031</v>
       </c>
       <c r="E51" t="n">
-        <v>7138</v>
+        <v>2104</v>
       </c>
       <c r="F51" t="n">
-        <v>28.3986473045554</v>
+        <v>8.370797692460712</v>
       </c>
       <c r="G51" t="n">
         <v>1.221034734029633</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8742773864464416</v>
+        <v>1.118824386689337</v>
       </c>
       <c r="I51" t="n">
-        <v>12294</v>
+        <v>18942</v>
       </c>
     </row>
     <row r="52">
@@ -2026,22 +2026,22 @@
         <v>56331</v>
       </c>
       <c r="D52" t="n">
-        <v>49616</v>
+        <v>52540</v>
       </c>
       <c r="E52" t="n">
-        <v>6715</v>
+        <v>3791</v>
       </c>
       <c r="F52" t="n">
-        <v>11.92061209635902</v>
+        <v>6.729864550602688</v>
       </c>
       <c r="G52" t="n">
         <v>1.196546157440843</v>
       </c>
       <c r="H52" t="n">
-        <v>1.053910531458431</v>
+        <v>1.116020221759633</v>
       </c>
       <c r="I52" t="n">
-        <v>39266</v>
+        <v>44331</v>
       </c>
     </row>
     <row r="53">
@@ -2057,22 +2057,22 @@
         <v>61866</v>
       </c>
       <c r="D53" t="n">
-        <v>55823</v>
+        <v>58323</v>
       </c>
       <c r="E53" t="n">
-        <v>6043</v>
+        <v>3543</v>
       </c>
       <c r="F53" t="n">
-        <v>9.76788542979989</v>
+        <v>5.726893608767336</v>
       </c>
       <c r="G53" t="n">
         <v>1.15973380822945</v>
       </c>
       <c r="H53" t="n">
-        <v>1.046452338550942</v>
+        <v>1.093317086887243</v>
       </c>
       <c r="I53" t="n">
-        <v>45881</v>
+        <v>50462</v>
       </c>
     </row>
     <row r="54">
@@ -2088,22 +2088,22 @@
         <v>42632</v>
       </c>
       <c r="D54" t="n">
-        <v>37664</v>
+        <v>40864</v>
       </c>
       <c r="E54" t="n">
-        <v>4968</v>
+        <v>1768</v>
       </c>
       <c r="F54" t="n">
-        <v>11.65321823981985</v>
+        <v>4.147119534621881</v>
       </c>
       <c r="G54" t="n">
         <v>1.286265990827902</v>
       </c>
       <c r="H54" t="n">
-        <v>1.136374607772146</v>
+        <v>1.232923002655081</v>
       </c>
       <c r="I54" t="n">
-        <v>29481</v>
+        <v>35289</v>
       </c>
     </row>
     <row r="55">
@@ -2119,22 +2119,22 @@
         <v>51794</v>
       </c>
       <c r="D55" t="n">
-        <v>46967</v>
+        <v>49295</v>
       </c>
       <c r="E55" t="n">
-        <v>4827</v>
+        <v>2499</v>
       </c>
       <c r="F55" t="n">
-        <v>9.319612310306214</v>
+        <v>4.824883191103217</v>
       </c>
       <c r="G55" t="n">
         <v>1.120209360671338</v>
       </c>
       <c r="H55" t="n">
-        <v>1.01581019119301</v>
+        <v>1.066160567523142</v>
       </c>
       <c r="I55" t="n">
-        <v>38308</v>
+        <v>43038</v>
       </c>
     </row>
     <row r="56">
@@ -2150,22 +2150,22 @@
         <v>62869</v>
       </c>
       <c r="D56" t="n">
-        <v>58158</v>
+        <v>59771</v>
       </c>
       <c r="E56" t="n">
-        <v>4711</v>
+        <v>3098</v>
       </c>
       <c r="F56" t="n">
-        <v>7.493359207240452</v>
+        <v>4.927706818940973</v>
       </c>
       <c r="G56" t="n">
         <v>1.092139320767828</v>
       </c>
       <c r="H56" t="n">
-        <v>1.010301398419178</v>
+        <v>1.038321896986016</v>
       </c>
       <c r="I56" t="n">
-        <v>49657</v>
+        <v>52803</v>
       </c>
     </row>
     <row r="57">
@@ -2181,22 +2181,22 @@
         <v>47450</v>
       </c>
       <c r="D57" t="n">
-        <v>38135</v>
+        <v>44794</v>
       </c>
       <c r="E57" t="n">
-        <v>9315</v>
+        <v>2656</v>
       </c>
       <c r="F57" t="n">
-        <v>19.63119072708114</v>
+        <v>5.597471022128556</v>
       </c>
       <c r="G57" t="n">
         <v>1.085092272862403</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8720757392119646</v>
+        <v>1.024354547325574</v>
       </c>
       <c r="I57" t="n">
-        <v>27775</v>
+        <v>37991</v>
       </c>
     </row>
     <row r="58">
@@ -2212,22 +2212,22 @@
         <v>49121</v>
       </c>
       <c r="D58" t="n">
-        <v>43935</v>
+        <v>46853</v>
       </c>
       <c r="E58" t="n">
-        <v>5186</v>
+        <v>2268</v>
       </c>
       <c r="F58" t="n">
-        <v>10.55760265466908</v>
+        <v>4.61716984589076</v>
       </c>
       <c r="G58" t="n">
         <v>1.290789646564183</v>
       </c>
       <c r="H58" t="n">
-        <v>1.154513204572329</v>
+        <v>1.231191696229142</v>
       </c>
       <c r="I58" t="n">
-        <v>35400</v>
+        <v>40781</v>
       </c>
     </row>
     <row r="59">
@@ -2243,22 +2243,22 @@
         <v>29291</v>
       </c>
       <c r="D59" t="n">
-        <v>26045</v>
+        <v>27300</v>
       </c>
       <c r="E59" t="n">
-        <v>3246</v>
+        <v>1991</v>
       </c>
       <c r="F59" t="n">
-        <v>11.08190229080605</v>
+        <v>6.797309753849305</v>
       </c>
       <c r="G59" t="n">
         <v>1.216706820636371</v>
       </c>
       <c r="H59" t="n">
-        <v>1.081872559607876</v>
+        <v>1.134003489241505</v>
       </c>
       <c r="I59" t="n">
-        <v>21014</v>
+        <v>23188</v>
       </c>
     </row>
     <row r="60">
@@ -2274,22 +2274,22 @@
         <v>52365</v>
       </c>
       <c r="D60" t="n">
-        <v>47412</v>
+        <v>49464</v>
       </c>
       <c r="E60" t="n">
-        <v>4953</v>
+        <v>2901</v>
       </c>
       <c r="F60" t="n">
-        <v>9.458607848753939</v>
+        <v>5.539959896877686</v>
       </c>
       <c r="G60" t="n">
         <v>1.167610595790225</v>
       </c>
       <c r="H60" t="n">
-        <v>1.057170888333928</v>
+        <v>1.102925437031752</v>
       </c>
       <c r="I60" t="n">
-        <v>38701</v>
+        <v>42628</v>
       </c>
     </row>
     <row r="61">
@@ -2305,22 +2305,22 @@
         <v>8898</v>
       </c>
       <c r="D61" t="n">
-        <v>6402</v>
+        <v>8059</v>
       </c>
       <c r="E61" t="n">
-        <v>2496</v>
+        <v>839</v>
       </c>
       <c r="F61" t="n">
-        <v>28.05124747134187</v>
+        <v>9.429085187682626</v>
       </c>
       <c r="G61" t="n">
         <v>1.720750338425836</v>
       </c>
       <c r="H61" t="n">
-        <v>1.238058402630052</v>
+        <v>1.558499323148327</v>
       </c>
       <c r="I61" t="n">
-        <v>4622</v>
+        <v>6675</v>
       </c>
     </row>
     <row r="62">
@@ -2336,22 +2336,22 @@
         <v>25270</v>
       </c>
       <c r="D62" t="n">
-        <v>21061</v>
+        <v>24160</v>
       </c>
       <c r="E62" t="n">
-        <v>4209</v>
+        <v>1110</v>
       </c>
       <c r="F62" t="n">
-        <v>16.65611396913336</v>
+        <v>4.392560348239019</v>
       </c>
       <c r="G62" t="n">
         <v>1.135271126285997</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9461790736331371</v>
+        <v>1.085403656947751</v>
       </c>
       <c r="I62" t="n">
-        <v>15908</v>
+        <v>20708</v>
       </c>
     </row>
     <row r="63">
@@ -2367,22 +2367,22 @@
         <v>18054</v>
       </c>
       <c r="D63" t="n">
-        <v>16373</v>
+        <v>17201</v>
       </c>
       <c r="E63" t="n">
-        <v>1681</v>
+        <v>853</v>
       </c>
       <c r="F63" t="n">
-        <v>9.31095602082641</v>
+        <v>4.724714744654924</v>
       </c>
       <c r="G63" t="n">
         <v>1.201757305464954</v>
       </c>
       <c r="H63" t="n">
-        <v>1.089862211276043</v>
+        <v>1.144977700858683</v>
       </c>
       <c r="I63" t="n">
-        <v>13376</v>
+        <v>14913</v>
       </c>
     </row>
     <row r="64">
@@ -2398,22 +2398,22 @@
         <v>61880</v>
       </c>
       <c r="D64" t="n">
-        <v>56799</v>
+        <v>59161</v>
       </c>
       <c r="E64" t="n">
-        <v>5081</v>
+        <v>2719</v>
       </c>
       <c r="F64" t="n">
-        <v>8.211053652230122</v>
+        <v>4.393988364576599</v>
       </c>
       <c r="G64" t="n">
         <v>1.156808494728184</v>
       </c>
       <c r="H64" t="n">
-        <v>1.061822328572497</v>
+        <v>1.105978464069393</v>
       </c>
       <c r="I64" t="n">
-        <v>47380</v>
+        <v>52185</v>
       </c>
     </row>
     <row r="65">
@@ -2429,22 +2429,22 @@
         <v>15813</v>
       </c>
       <c r="D65" t="n">
-        <v>14308</v>
+        <v>15118</v>
       </c>
       <c r="E65" t="n">
-        <v>1505</v>
+        <v>695</v>
       </c>
       <c r="F65" t="n">
-        <v>9.517485613103142</v>
+        <v>4.395117940934674</v>
       </c>
       <c r="G65" t="n">
         <v>1.130388162127386</v>
       </c>
       <c r="H65" t="n">
-        <v>1.022803631424691</v>
+        <v>1.080706269211523</v>
       </c>
       <c r="I65" t="n">
-        <v>11621</v>
+        <v>13223</v>
       </c>
     </row>
     <row r="66">
@@ -2460,22 +2460,22 @@
         <v>89002</v>
       </c>
       <c r="D66" t="n">
-        <v>83294</v>
+        <v>85314</v>
       </c>
       <c r="E66" t="n">
-        <v>5708</v>
+        <v>3688</v>
       </c>
       <c r="F66" t="n">
-        <v>6.413339026089301</v>
+        <v>4.143727107256017</v>
       </c>
       <c r="G66" t="n">
         <v>1.191682510778459</v>
       </c>
       <c r="H66" t="n">
-        <v>1.115255871247623</v>
+        <v>1.142302439546903</v>
       </c>
       <c r="I66" t="n">
-        <v>72733</v>
+        <v>76712</v>
       </c>
     </row>
     <row r="67">
@@ -2491,22 +2491,22 @@
         <v>14317</v>
       </c>
       <c r="D67" t="n">
-        <v>9658</v>
+        <v>13130</v>
       </c>
       <c r="E67" t="n">
-        <v>4659</v>
+        <v>1187</v>
       </c>
       <c r="F67" t="n">
-        <v>32.54173360340854</v>
+        <v>8.29084305371237</v>
       </c>
       <c r="G67" t="n">
         <v>1.103940165008867</v>
       </c>
       <c r="H67" t="n">
-        <v>0.7446988973706531</v>
+        <v>1.012414218521089</v>
       </c>
       <c r="I67" t="n">
-        <v>6668</v>
+        <v>10576</v>
       </c>
     </row>
     <row r="68">
@@ -2522,22 +2522,22 @@
         <v>82511</v>
       </c>
       <c r="D68" t="n">
-        <v>70327</v>
+        <v>77685</v>
       </c>
       <c r="E68" t="n">
-        <v>12184</v>
+        <v>4826</v>
       </c>
       <c r="F68" t="n">
-        <v>14.76651597968756</v>
+        <v>5.848917114081758</v>
       </c>
       <c r="G68" t="n">
         <v>1.132521686614692</v>
       </c>
       <c r="H68" t="n">
-        <v>0.9652876907873065</v>
+        <v>1.066281431865598</v>
       </c>
       <c r="I68" t="n">
-        <v>52934</v>
+        <v>65229</v>
       </c>
     </row>
     <row r="69">
@@ -2553,22 +2553,22 @@
         <v>40355</v>
       </c>
       <c r="D69" t="n">
-        <v>35582</v>
+        <v>37422</v>
       </c>
       <c r="E69" t="n">
-        <v>4773</v>
+        <v>2933</v>
       </c>
       <c r="F69" t="n">
-        <v>11.82753066534506</v>
+        <v>7.267996530789246</v>
       </c>
       <c r="G69" t="n">
         <v>1.408994099368039</v>
       </c>
       <c r="H69" t="n">
-        <v>1.242344890192381</v>
+        <v>1.306588457106945</v>
       </c>
       <c r="I69" t="n">
-        <v>28444</v>
+        <v>31610</v>
       </c>
     </row>
     <row r="70">
@@ -2584,22 +2584,22 @@
         <v>23619</v>
       </c>
       <c r="D70" t="n">
-        <v>16115</v>
+        <v>21065</v>
       </c>
       <c r="E70" t="n">
-        <v>7504</v>
+        <v>2554</v>
       </c>
       <c r="F70" t="n">
-        <v>31.77103179643507</v>
+        <v>10.81332825267793</v>
       </c>
       <c r="G70" t="n">
         <v>1.162695677857635</v>
       </c>
       <c r="H70" t="n">
-        <v>0.7932952643497095</v>
+        <v>1.03696957763119</v>
       </c>
       <c r="I70" t="n">
-        <v>11187</v>
+        <v>16645</v>
       </c>
     </row>
     <row r="71">
@@ -2615,22 +2615,22 @@
         <v>48786</v>
       </c>
       <c r="D71" t="n">
-        <v>44428</v>
+        <v>46372</v>
       </c>
       <c r="E71" t="n">
-        <v>4358</v>
+        <v>2414</v>
       </c>
       <c r="F71" t="n">
-        <v>8.932890583364079</v>
+        <v>4.948140860082811</v>
       </c>
       <c r="G71" t="n">
         <v>1.014599450960818</v>
       </c>
       <c r="H71" t="n">
-        <v>0.923966392147076</v>
+        <v>0.9643956409616504</v>
       </c>
       <c r="I71" t="n">
-        <v>36370</v>
+        <v>39920</v>
       </c>
     </row>
     <row r="72">
@@ -2646,22 +2646,22 @@
         <v>22262</v>
       </c>
       <c r="D72" t="n">
-        <v>17295</v>
+        <v>20687</v>
       </c>
       <c r="E72" t="n">
-        <v>4967</v>
+        <v>1575</v>
       </c>
       <c r="F72" t="n">
-        <v>22.31156230347678</v>
+        <v>7.074836043482168</v>
       </c>
       <c r="G72" t="n">
         <v>1.193289022298456</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9270475986277873</v>
+        <v>1.108865780445969</v>
       </c>
       <c r="I72" t="n">
-        <v>12473</v>
+        <v>17349</v>
       </c>
     </row>
     <row r="73">
@@ -2677,22 +2677,22 @@
         <v>9548</v>
       </c>
       <c r="D73" t="n">
-        <v>8913</v>
+        <v>9100</v>
       </c>
       <c r="E73" t="n">
-        <v>635</v>
+        <v>448</v>
       </c>
       <c r="F73" t="n">
-        <v>6.65060745705907</v>
+        <v>4.69208211143695</v>
       </c>
       <c r="G73" t="n">
         <v>1.500785916378497</v>
       </c>
       <c r="H73" t="n">
-        <v>1.400974536309337</v>
+        <v>1.430367808865137</v>
       </c>
       <c r="I73" t="n">
-        <v>7330</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="74">
@@ -2708,22 +2708,22 @@
         <v>79175</v>
       </c>
       <c r="D74" t="n">
-        <v>72841</v>
+        <v>76359</v>
       </c>
       <c r="E74" t="n">
-        <v>6334</v>
+        <v>2816</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>3.556678244395327</v>
       </c>
       <c r="G74" t="n">
         <v>1.134312320916905</v>
       </c>
       <c r="H74" t="n">
-        <v>1.043567335243553</v>
+        <v>1.093968481375358</v>
       </c>
       <c r="I74" t="n">
-        <v>58575</v>
+        <v>67089</v>
       </c>
     </row>
     <row r="75">
@@ -2739,22 +2739,22 @@
         <v>9775</v>
       </c>
       <c r="D75" t="n">
-        <v>7872</v>
+        <v>9024</v>
       </c>
       <c r="E75" t="n">
-        <v>1903</v>
+        <v>751</v>
       </c>
       <c r="F75" t="n">
-        <v>19.46803069053708</v>
+        <v>7.682864450127877</v>
       </c>
       <c r="G75" t="n">
         <v>1.62106135986733</v>
       </c>
       <c r="H75" t="n">
-        <v>1.30547263681592</v>
+        <v>1.496517412935323</v>
       </c>
       <c r="I75" t="n">
-        <v>5750</v>
+        <v>7383</v>
       </c>
     </row>
     <row r="76">
@@ -2770,22 +2770,22 @@
         <v>7002</v>
       </c>
       <c r="D76" t="n">
-        <v>6490</v>
+        <v>6663</v>
       </c>
       <c r="E76" t="n">
-        <v>512</v>
+        <v>339</v>
       </c>
       <c r="F76" t="n">
-        <v>7.312196515281348</v>
+        <v>4.841473864610111</v>
       </c>
       <c r="G76" t="n">
         <v>1.447890818858561</v>
       </c>
       <c r="H76" t="n">
-        <v>1.342018196856906</v>
+        <v>1.377791563275434</v>
       </c>
       <c r="I76" t="n">
-        <v>5277</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="77">
@@ -2801,22 +2801,22 @@
         <v>40624</v>
       </c>
       <c r="D77" t="n">
-        <v>37569</v>
+        <v>38615</v>
       </c>
       <c r="E77" t="n">
-        <v>3055</v>
+        <v>2009</v>
       </c>
       <c r="F77" t="n">
-        <v>7.520185112248917</v>
+        <v>4.94535250098464</v>
       </c>
       <c r="G77" t="n">
         <v>1.890807540144287</v>
       </c>
       <c r="H77" t="n">
-        <v>1.748615313009076</v>
+        <v>1.797300442168955</v>
       </c>
       <c r="I77" t="n">
-        <v>31471</v>
+        <v>34004</v>
       </c>
     </row>
     <row r="78">
@@ -2832,22 +2832,22 @@
         <v>10749</v>
       </c>
       <c r="D78" t="n">
-        <v>8455</v>
+        <v>10265</v>
       </c>
       <c r="E78" t="n">
-        <v>2294</v>
+        <v>484</v>
       </c>
       <c r="F78" t="n">
-        <v>21.34152014140851</v>
+        <v>4.50274444134338</v>
       </c>
       <c r="G78" t="n">
         <v>1.270116979794399</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9990547087321281</v>
+        <v>1.212926858088148</v>
       </c>
       <c r="I78" t="n">
-        <v>6233</v>
+        <v>8783</v>
       </c>
     </row>
     <row r="79">
@@ -2863,22 +2863,22 @@
         <v>38457</v>
       </c>
       <c r="D79" t="n">
-        <v>35789</v>
+        <v>37103</v>
       </c>
       <c r="E79" t="n">
-        <v>2668</v>
+        <v>1354</v>
       </c>
       <c r="F79" t="n">
-        <v>6.937618638999401</v>
+        <v>3.520815456223835</v>
       </c>
       <c r="G79" t="n">
         <v>1.235883921971912</v>
       </c>
       <c r="H79" t="n">
-        <v>1.150143008644792</v>
+        <v>1.19237072982614</v>
       </c>
       <c r="I79" t="n">
-        <v>29465</v>
+        <v>32724</v>
       </c>
     </row>
     <row r="80">
@@ -2894,22 +2894,22 @@
         <v>19119</v>
       </c>
       <c r="D80" t="n">
-        <v>9574</v>
+        <v>17266</v>
       </c>
       <c r="E80" t="n">
-        <v>9545</v>
+        <v>1853</v>
       </c>
       <c r="F80" t="n">
-        <v>49.92415921334798</v>
+        <v>9.69192949422041</v>
       </c>
       <c r="G80" t="n">
         <v>1.400659340659341</v>
       </c>
       <c r="H80" t="n">
-        <v>0.7013919413919414</v>
+        <v>1.264908424908425</v>
       </c>
       <c r="I80" t="n">
-        <v>5630</v>
+        <v>13131</v>
       </c>
     </row>
     <row r="81">
@@ -2925,22 +2925,22 @@
         <v>27747</v>
       </c>
       <c r="D81" t="n">
-        <v>12843</v>
+        <v>25885</v>
       </c>
       <c r="E81" t="n">
-        <v>14904</v>
+        <v>1862</v>
       </c>
       <c r="F81" t="n">
-        <v>53.71391501783977</v>
+        <v>6.710635384005478</v>
       </c>
       <c r="G81" t="n">
         <v>1.235011349979971</v>
       </c>
       <c r="H81" t="n">
-        <v>0.5716384029910535</v>
+        <v>1.152134241331731</v>
       </c>
       <c r="I81" t="n">
-        <v>7647</v>
+        <v>20544</v>
       </c>
     </row>
     <row r="82">
@@ -2956,22 +2956,22 @@
         <v>10184</v>
       </c>
       <c r="D82" t="n">
-        <v>7929</v>
+        <v>9523</v>
       </c>
       <c r="E82" t="n">
-        <v>2255</v>
+        <v>661</v>
       </c>
       <c r="F82" t="n">
-        <v>22.14257659073056</v>
+        <v>6.49057344854674</v>
       </c>
       <c r="G82" t="n">
         <v>1.224921818619197</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9536925667548714</v>
+        <v>1.145417368294443</v>
       </c>
       <c r="I82" t="n">
-        <v>5669</v>
+        <v>7842</v>
       </c>
     </row>
     <row r="83">
@@ -2987,22 +2987,22 @@
         <v>7294</v>
       </c>
       <c r="D83" t="n">
-        <v>5908</v>
+        <v>6905</v>
       </c>
       <c r="E83" t="n">
-        <v>1386</v>
+        <v>389</v>
       </c>
       <c r="F83" t="n">
-        <v>19.00191938579654</v>
+        <v>5.333150534686043</v>
       </c>
       <c r="G83" t="n">
         <v>1.263467867659796</v>
       </c>
       <c r="H83" t="n">
-        <v>1.023384721981639</v>
+        <v>1.196085224320111</v>
       </c>
       <c r="I83" t="n">
-        <v>4556</v>
+        <v>5948</v>
       </c>
     </row>
     <row r="84">
@@ -3018,22 +3018,22 @@
         <v>8679</v>
       </c>
       <c r="D84" t="n">
-        <v>6230</v>
+        <v>8120</v>
       </c>
       <c r="E84" t="n">
-        <v>2449</v>
+        <v>559</v>
       </c>
       <c r="F84" t="n">
-        <v>28.21753658255559</v>
+        <v>6.440834197488191</v>
       </c>
       <c r="G84" t="n">
         <v>1.259834518798084</v>
       </c>
       <c r="H84" t="n">
-        <v>0.9043402525765714</v>
+        <v>1.178690666279576</v>
       </c>
       <c r="I84" t="n">
-        <v>4141</v>
+        <v>6597</v>
       </c>
     </row>
     <row r="85">
@@ -3049,22 +3049,22 @@
         <v>25612</v>
       </c>
       <c r="D85" t="n">
-        <v>22576</v>
+        <v>24437</v>
       </c>
       <c r="E85" t="n">
-        <v>3036</v>
+        <v>1175</v>
       </c>
       <c r="F85" t="n">
-        <v>11.85381852256755</v>
+        <v>4.587693268780259</v>
       </c>
       <c r="G85" t="n">
         <v>1.430118934613881</v>
       </c>
       <c r="H85" t="n">
-        <v>1.260595231447875</v>
+        <v>1.364509464515048</v>
       </c>
       <c r="I85" t="n">
-        <v>16882</v>
+        <v>20899</v>
       </c>
     </row>
     <row r="86">
@@ -3080,22 +3080,22 @@
         <v>14531</v>
       </c>
       <c r="D86" t="n">
-        <v>12448</v>
+        <v>13827</v>
       </c>
       <c r="E86" t="n">
-        <v>2083</v>
+        <v>704</v>
       </c>
       <c r="F86" t="n">
-        <v>14.3348702773381</v>
+        <v>4.844814534443604</v>
       </c>
       <c r="G86" t="n">
         <v>1.257224433292957</v>
       </c>
       <c r="H86" t="n">
-        <v>1.077002941685413</v>
+        <v>1.196314241218204</v>
       </c>
       <c r="I86" t="n">
-        <v>9029</v>
+        <v>11767</v>
       </c>
     </row>
     <row r="87">
@@ -3111,22 +3111,22 @@
         <v>36145</v>
       </c>
       <c r="D87" t="n">
-        <v>31959</v>
+        <v>33821</v>
       </c>
       <c r="E87" t="n">
-        <v>4186</v>
+        <v>2324</v>
       </c>
       <c r="F87" t="n">
-        <v>11.58113155346521</v>
+        <v>6.429658320652925</v>
       </c>
       <c r="G87" t="n">
         <v>1.250562225374529</v>
       </c>
       <c r="H87" t="n">
-        <v>1.105732968895962</v>
+        <v>1.170155347195793</v>
       </c>
       <c r="I87" t="n">
-        <v>24424</v>
+        <v>27707</v>
       </c>
     </row>
     <row r="88">
@@ -3142,22 +3142,22 @@
         <v>16381</v>
       </c>
       <c r="D88" t="n">
-        <v>11028</v>
+        <v>14729</v>
       </c>
       <c r="E88" t="n">
-        <v>5353</v>
+        <v>1652</v>
       </c>
       <c r="F88" t="n">
-        <v>32.67810267993407</v>
+        <v>10.08485440449301</v>
       </c>
       <c r="G88" t="n">
         <v>1.365197099758313</v>
       </c>
       <c r="H88" t="n">
-        <v>0.9190765897158096</v>
+        <v>1.227518959913326</v>
       </c>
       <c r="I88" t="n">
-        <v>7309</v>
+        <v>11671</v>
       </c>
     </row>
     <row r="89">
@@ -3173,22 +3173,22 @@
         <v>13432</v>
       </c>
       <c r="D89" t="n">
-        <v>12074</v>
+        <v>12811</v>
       </c>
       <c r="E89" t="n">
-        <v>1358</v>
+        <v>621</v>
       </c>
       <c r="F89" t="n">
-        <v>10.11018463371054</v>
+        <v>4.623287671232877</v>
       </c>
       <c r="G89" t="n">
         <v>1.376511580241853</v>
       </c>
       <c r="H89" t="n">
-        <v>1.237343717974995</v>
+        <v>1.312871490059438</v>
       </c>
       <c r="I89" t="n">
-        <v>9446</v>
+        <v>10777</v>
       </c>
     </row>
     <row r="90">
@@ -3204,22 +3204,22 @@
         <v>13532</v>
       </c>
       <c r="D90" t="n">
-        <v>11929</v>
+        <v>12951</v>
       </c>
       <c r="E90" t="n">
-        <v>1603</v>
+        <v>581</v>
       </c>
       <c r="F90" t="n">
-        <v>11.84599467927875</v>
+        <v>4.293526455808454</v>
       </c>
       <c r="G90" t="n">
         <v>1.132384937238494</v>
       </c>
       <c r="H90" t="n">
-        <v>0.9982426778242678</v>
+        <v>1.083765690376569</v>
       </c>
       <c r="I90" t="n">
-        <v>9755</v>
+        <v>11430</v>
       </c>
     </row>
     <row r="91">
@@ -3235,22 +3235,22 @@
         <v>6240</v>
       </c>
       <c r="D91" t="n">
-        <v>5796</v>
+        <v>5973</v>
       </c>
       <c r="E91" t="n">
-        <v>444</v>
+        <v>267</v>
       </c>
       <c r="F91" t="n">
-        <v>7.115384615384615</v>
+        <v>4.278846153846154</v>
       </c>
       <c r="G91" t="n">
         <v>1.402247191011236</v>
       </c>
       <c r="H91" t="n">
-        <v>1.30247191011236</v>
+        <v>1.342247191011236</v>
       </c>
       <c r="I91" t="n">
-        <v>4864</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="92">
@@ -3266,22 +3266,22 @@
         <v>6722</v>
       </c>
       <c r="D92" t="n">
-        <v>6111</v>
+        <v>6466</v>
       </c>
       <c r="E92" t="n">
-        <v>611</v>
+        <v>256</v>
       </c>
       <c r="F92" t="n">
-        <v>9.089556679559655</v>
+        <v>3.808390360011901</v>
       </c>
       <c r="G92" t="n">
         <v>1.776896642876024</v>
       </c>
       <c r="H92" t="n">
-        <v>1.615384615384615</v>
+        <v>1.709225482421359</v>
       </c>
       <c r="I92" t="n">
-        <v>4961</v>
+        <v>5751</v>
       </c>
     </row>
     <row r="93">
@@ -3297,22 +3297,22 @@
         <v>8152</v>
       </c>
       <c r="D93" t="n">
-        <v>7591</v>
+        <v>7798</v>
       </c>
       <c r="E93" t="n">
-        <v>561</v>
+        <v>354</v>
       </c>
       <c r="F93" t="n">
-        <v>6.881746810598625</v>
+        <v>4.342492639842983</v>
       </c>
       <c r="G93" t="n">
         <v>1.483530482256597</v>
       </c>
       <c r="H93" t="n">
-        <v>1.381437670609645</v>
+        <v>1.419108280254777</v>
       </c>
       <c r="I93" t="n">
-        <v>6282</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="94">
@@ -3328,22 +3328,22 @@
         <v>6941</v>
       </c>
       <c r="D94" t="n">
-        <v>5578</v>
+        <v>6393</v>
       </c>
       <c r="E94" t="n">
-        <v>1363</v>
+        <v>548</v>
       </c>
       <c r="F94" t="n">
-        <v>19.63693992220141</v>
+        <v>7.895115977524853</v>
       </c>
       <c r="G94" t="n">
         <v>1.35911494027805</v>
       </c>
       <c r="H94" t="n">
-        <v>1.092226355981986</v>
+        <v>1.25181123947523</v>
       </c>
       <c r="I94" t="n">
-        <v>3974</v>
+        <v>5088</v>
       </c>
     </row>
     <row r="95">
@@ -3359,22 +3359,22 @@
         <v>8019</v>
       </c>
       <c r="D95" t="n">
-        <v>5748</v>
+        <v>7402</v>
       </c>
       <c r="E95" t="n">
-        <v>2271</v>
+        <v>617</v>
       </c>
       <c r="F95" t="n">
-        <v>28.32023943135054</v>
+        <v>7.694226212744732</v>
       </c>
       <c r="G95" t="n">
         <v>1.449042284062161</v>
       </c>
       <c r="H95" t="n">
-        <v>1.038670039754247</v>
+        <v>1.337549692808095</v>
       </c>
       <c r="I95" t="n">
-        <v>3787</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="96">
@@ -3390,22 +3390,22 @@
         <v>22603</v>
       </c>
       <c r="D96" t="n">
-        <v>15016</v>
+        <v>21181</v>
       </c>
       <c r="E96" t="n">
-        <v>7587</v>
+        <v>1422</v>
       </c>
       <c r="F96" t="n">
-        <v>33.56634075122771</v>
+        <v>6.291200283148254</v>
       </c>
       <c r="G96" t="n">
         <v>1.083505105220268</v>
       </c>
       <c r="H96" t="n">
-        <v>0.7198120895450841</v>
+        <v>1.015339628972724</v>
       </c>
       <c r="I96" t="n">
-        <v>10023</v>
+        <v>17366</v>
       </c>
     </row>
     <row r="97">
@@ -3421,22 +3421,22 @@
         <v>11625</v>
       </c>
       <c r="D97" t="n">
-        <v>6498</v>
+        <v>10798</v>
       </c>
       <c r="E97" t="n">
-        <v>5127</v>
+        <v>827</v>
       </c>
       <c r="F97" t="n">
-        <v>44.10322580645161</v>
+        <v>7.113978494623656</v>
       </c>
       <c r="G97" t="n">
         <v>1.166817223727793</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6522131887985546</v>
+        <v>1.083810097360233</v>
       </c>
       <c r="I97" t="n">
-        <v>4554</v>
+        <v>8819</v>
       </c>
     </row>
     <row r="98">
@@ -3452,22 +3452,22 @@
         <v>46985</v>
       </c>
       <c r="D98" t="n">
-        <v>39005</v>
+        <v>43377</v>
       </c>
       <c r="E98" t="n">
-        <v>7980</v>
+        <v>3608</v>
       </c>
       <c r="F98" t="n">
-        <v>16.98414387570501</v>
+        <v>7.67904650420347</v>
       </c>
       <c r="G98" t="n">
         <v>1.213925849373466</v>
       </c>
       <c r="H98" t="n">
-        <v>1.007750936571502</v>
+        <v>1.12070791887353</v>
       </c>
       <c r="I98" t="n">
-        <v>28307</v>
+        <v>35271</v>
       </c>
     </row>
     <row r="99">
@@ -3483,22 +3483,22 @@
         <v>37933</v>
       </c>
       <c r="D99" t="n">
-        <v>26090</v>
+        <v>36150</v>
       </c>
       <c r="E99" t="n">
-        <v>11843</v>
+        <v>1783</v>
       </c>
       <c r="F99" t="n">
-        <v>31.22083673845992</v>
+        <v>4.700392797827749</v>
       </c>
       <c r="G99" t="n">
         <v>1.244520997375328</v>
       </c>
       <c r="H99" t="n">
-        <v>0.8559711286089239</v>
+        <v>1.186023622047244</v>
       </c>
       <c r="I99" t="n">
-        <v>19235</v>
+        <v>29916</v>
       </c>
     </row>
     <row r="100">
@@ -3514,22 +3514,22 @@
         <v>10098</v>
       </c>
       <c r="D100" t="n">
-        <v>9441</v>
+        <v>9643</v>
       </c>
       <c r="E100" t="n">
-        <v>657</v>
+        <v>455</v>
       </c>
       <c r="F100" t="n">
-        <v>6.506238859180035</v>
+        <v>4.505842741136859</v>
       </c>
       <c r="G100" t="n">
         <v>1.438256658595642</v>
       </c>
       <c r="H100" t="n">
-        <v>1.344680244979348</v>
+        <v>1.373451075345392</v>
       </c>
       <c r="I100" t="n">
-        <v>7869</v>
+        <v>8554</v>
       </c>
     </row>
     <row r="101">
@@ -3545,22 +3545,22 @@
         <v>9665</v>
       </c>
       <c r="D101" t="n">
-        <v>8908</v>
+        <v>9242</v>
       </c>
       <c r="E101" t="n">
-        <v>757</v>
+        <v>423</v>
       </c>
       <c r="F101" t="n">
-        <v>7.832384893947232</v>
+        <v>4.37661665804449</v>
       </c>
       <c r="G101" t="n">
         <v>1.380122804512352</v>
       </c>
       <c r="H101" t="n">
-        <v>1.272026274453806</v>
+        <v>1.319720119948594</v>
       </c>
       <c r="I101" t="n">
-        <v>7449</v>
+        <v>8152</v>
       </c>
     </row>
     <row r="102">
@@ -3576,22 +3576,22 @@
         <v>61515</v>
       </c>
       <c r="D102" t="n">
-        <v>52940</v>
+        <v>58591</v>
       </c>
       <c r="E102" t="n">
-        <v>8575</v>
+        <v>2924</v>
       </c>
       <c r="F102" t="n">
-        <v>13.9396895066244</v>
+        <v>4.753312200276355</v>
       </c>
       <c r="G102" t="n">
         <v>1.181503889369058</v>
       </c>
       <c r="H102" t="n">
-        <v>1.01680591568232</v>
+        <v>1.125343320848939</v>
       </c>
       <c r="I102" t="n">
-        <v>39865</v>
+        <v>49443</v>
       </c>
     </row>
     <row r="103">
@@ -3607,22 +3607,22 @@
         <v>8855</v>
       </c>
       <c r="D103" t="n">
-        <v>8321</v>
+        <v>8479</v>
       </c>
       <c r="E103" t="n">
-        <v>534</v>
+        <v>376</v>
       </c>
       <c r="F103" t="n">
-        <v>6.030491247882552</v>
+        <v>4.246188594014681</v>
       </c>
       <c r="G103" t="n">
         <v>1.414988814317673</v>
       </c>
       <c r="H103" t="n">
-        <v>1.329658037711729</v>
+        <v>1.354905720677533</v>
       </c>
       <c r="I103" t="n">
-        <v>7127</v>
+        <v>7614</v>
       </c>
     </row>
     <row r="104">
@@ -3638,22 +3638,22 @@
         <v>24935</v>
       </c>
       <c r="D104" t="n">
-        <v>16240</v>
+        <v>23374</v>
       </c>
       <c r="E104" t="n">
-        <v>8695</v>
+        <v>1561</v>
       </c>
       <c r="F104" t="n">
-        <v>34.87066372568678</v>
+        <v>6.260276719470624</v>
       </c>
       <c r="G104" t="n">
         <v>1.073119297641591</v>
       </c>
       <c r="H104" t="n">
-        <v>0.6989154759855397</v>
+        <v>1.005939060079188</v>
       </c>
       <c r="I104" t="n">
-        <v>10289</v>
+        <v>18698</v>
       </c>
     </row>
     <row r="105">
@@ -3669,22 +3669,22 @@
         <v>13773</v>
       </c>
       <c r="D105" t="n">
-        <v>12137</v>
+        <v>12678</v>
       </c>
       <c r="E105" t="n">
-        <v>1636</v>
+        <v>1095</v>
       </c>
       <c r="F105" t="n">
-        <v>11.87831264067378</v>
+        <v>7.95033761707689</v>
       </c>
       <c r="G105" t="n">
         <v>1.399410688884373</v>
       </c>
       <c r="H105" t="n">
-        <v>1.233184312131681</v>
+        <v>1.288152814468604</v>
       </c>
       <c r="I105" t="n">
-        <v>9648</v>
+        <v>10802</v>
       </c>
     </row>
     <row r="106">
@@ -3700,22 +3700,22 @@
         <v>7823</v>
       </c>
       <c r="D106" t="n">
-        <v>7025</v>
+        <v>7351</v>
       </c>
       <c r="E106" t="n">
-        <v>798</v>
+        <v>472</v>
       </c>
       <c r="F106" t="n">
-        <v>10.20069027227406</v>
+        <v>6.033490988111978</v>
       </c>
       <c r="G106" t="n">
         <v>1.360995128740431</v>
       </c>
       <c r="H106" t="n">
-        <v>1.222164231036882</v>
+        <v>1.278879610299235</v>
       </c>
       <c r="I106" t="n">
-        <v>5599</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="107">
@@ -3731,22 +3731,22 @@
         <v>35436</v>
       </c>
       <c r="D107" t="n">
-        <v>32646</v>
+        <v>33694</v>
       </c>
       <c r="E107" t="n">
-        <v>2790</v>
+        <v>1742</v>
       </c>
       <c r="F107" t="n">
-        <v>7.873349136471385</v>
+        <v>4.91590472965346</v>
       </c>
       <c r="G107" t="n">
         <v>1.252465274096066</v>
       </c>
       <c r="H107" t="n">
-        <v>1.15385431025342</v>
+        <v>1.19089527444951</v>
       </c>
       <c r="I107" t="n">
-        <v>27047</v>
+        <v>29430</v>
       </c>
     </row>
     <row r="108">
@@ -3762,22 +3762,22 @@
         <v>26432</v>
       </c>
       <c r="D108" t="n">
-        <v>21601</v>
+        <v>24894</v>
       </c>
       <c r="E108" t="n">
-        <v>4831</v>
+        <v>1538</v>
       </c>
       <c r="F108" t="n">
-        <v>18.27708837772397</v>
+        <v>5.818704600484261</v>
       </c>
       <c r="G108" t="n">
         <v>1.102941790110578</v>
       </c>
       <c r="H108" t="n">
-        <v>0.9013561443772168</v>
+        <v>1.03876486542875</v>
       </c>
       <c r="I108" t="n">
-        <v>16438</v>
+        <v>21244</v>
       </c>
     </row>
     <row r="109">
@@ -3793,22 +3793,22 @@
         <v>8365</v>
       </c>
       <c r="D109" t="n">
-        <v>7669</v>
+        <v>7928</v>
       </c>
       <c r="E109" t="n">
-        <v>696</v>
+        <v>437</v>
       </c>
       <c r="F109" t="n">
-        <v>8.32038254632397</v>
+        <v>5.224148236700538</v>
       </c>
       <c r="G109" t="n">
         <v>1.232503315161338</v>
       </c>
       <c r="H109" t="n">
-        <v>1.12995432444379</v>
+        <v>1.168115514955061</v>
       </c>
       <c r="I109" t="n">
-        <v>6377</v>
+        <v>6908</v>
       </c>
     </row>
     <row r="110">
@@ -3824,22 +3824,22 @@
         <v>8837</v>
       </c>
       <c r="D110" t="n">
-        <v>6383</v>
+        <v>8056</v>
       </c>
       <c r="E110" t="n">
-        <v>2454</v>
+        <v>781</v>
       </c>
       <c r="F110" t="n">
-        <v>27.76960506959376</v>
+        <v>8.837840896231752</v>
       </c>
       <c r="G110" t="n">
         <v>1.481475272422464</v>
       </c>
       <c r="H110" t="n">
-        <v>1.070075440067058</v>
+        <v>1.350544844928751</v>
       </c>
       <c r="I110" t="n">
-        <v>4271</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="111">
@@ -3855,22 +3855,22 @@
         <v>20085</v>
       </c>
       <c r="D111" t="n">
-        <v>16857</v>
+        <v>18818</v>
       </c>
       <c r="E111" t="n">
-        <v>3228</v>
+        <v>1267</v>
       </c>
       <c r="F111" t="n">
-        <v>16.07169529499627</v>
+        <v>6.308190191685337</v>
       </c>
       <c r="G111" t="n">
         <v>1.138799115495833</v>
       </c>
       <c r="H111" t="n">
-        <v>0.9557747916312298</v>
+        <v>1.066961501389125</v>
       </c>
       <c r="I111" t="n">
-        <v>13122</v>
+        <v>16160</v>
       </c>
     </row>
     <row r="112">
@@ -3886,22 +3886,22 @@
         <v>7831</v>
       </c>
       <c r="D112" t="n">
-        <v>7068</v>
+        <v>7437</v>
       </c>
       <c r="E112" t="n">
-        <v>763</v>
+        <v>394</v>
       </c>
       <c r="F112" t="n">
-        <v>9.743327799770144</v>
+        <v>5.03128591495339</v>
       </c>
       <c r="G112" t="n">
         <v>1.489632870458436</v>
       </c>
       <c r="H112" t="n">
-        <v>1.344493056876546</v>
+        <v>1.414685181662545</v>
       </c>
       <c r="I112" t="n">
-        <v>5709</v>
+        <v>6503</v>
       </c>
     </row>
     <row r="113">
@@ -3917,22 +3917,22 @@
         <v>42197</v>
       </c>
       <c r="D113" t="n">
-        <v>38626</v>
+        <v>40194</v>
       </c>
       <c r="E113" t="n">
-        <v>3571</v>
+        <v>2003</v>
       </c>
       <c r="F113" t="n">
-        <v>8.462686920871151</v>
+        <v>4.746782946654975</v>
       </c>
       <c r="G113" t="n">
         <v>1.19150077650713</v>
       </c>
       <c r="H113" t="n">
-        <v>1.090667796131583</v>
+        <v>1.134942820838628</v>
       </c>
       <c r="I113" t="n">
-        <v>30955</v>
+        <v>35142</v>
       </c>
     </row>
     <row r="114">
@@ -3948,22 +3948,22 @@
         <v>83865</v>
       </c>
       <c r="D114" t="n">
-        <v>75427</v>
+        <v>79072</v>
       </c>
       <c r="E114" t="n">
-        <v>8438</v>
+        <v>4793</v>
       </c>
       <c r="F114" t="n">
-        <v>10.06140821558457</v>
+        <v>5.715137423239731</v>
       </c>
       <c r="G114" t="n">
         <v>1.280166689563585</v>
       </c>
       <c r="H114" t="n">
-        <v>1.151363893086657</v>
+        <v>1.207003404008487</v>
       </c>
       <c r="I114" t="n">
-        <v>59000</v>
+        <v>66564</v>
       </c>
     </row>
     <row r="115">
@@ -3979,22 +3979,22 @@
         <v>7887</v>
       </c>
       <c r="D115" t="n">
-        <v>5691</v>
+        <v>7325</v>
       </c>
       <c r="E115" t="n">
-        <v>2196</v>
+        <v>562</v>
       </c>
       <c r="F115" t="n">
-        <v>27.84328642069228</v>
+        <v>7.125649803474071</v>
       </c>
       <c r="G115" t="n">
         <v>1.319779116465863</v>
       </c>
       <c r="H115" t="n">
-        <v>0.9523092369477911</v>
+        <v>1.225736278447122</v>
       </c>
       <c r="I115" t="n">
-        <v>3738</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="116">
@@ -4010,22 +4010,22 @@
         <v>9065</v>
       </c>
       <c r="D116" t="n">
-        <v>8440</v>
+        <v>8610</v>
       </c>
       <c r="E116" t="n">
-        <v>625</v>
+        <v>455</v>
       </c>
       <c r="F116" t="n">
-        <v>6.894649751792609</v>
+        <v>5.019305019305019</v>
       </c>
       <c r="G116" t="n">
         <v>1.562392278524647</v>
       </c>
       <c r="H116" t="n">
-        <v>1.45467080317132</v>
+        <v>1.483971044467425</v>
       </c>
       <c r="I116" t="n">
-        <v>6986</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="117">
@@ -4041,22 +4041,22 @@
         <v>11609</v>
       </c>
       <c r="D117" t="n">
-        <v>9261</v>
+        <v>10834</v>
       </c>
       <c r="E117" t="n">
-        <v>2348</v>
+        <v>775</v>
       </c>
       <c r="F117" t="n">
-        <v>20.22568696700835</v>
+        <v>6.675854940132655</v>
       </c>
       <c r="G117" t="n">
         <v>1.354609101516919</v>
       </c>
       <c r="H117" t="n">
-        <v>1.080630105017503</v>
+        <v>1.264177362893816</v>
       </c>
       <c r="I117" t="n">
-        <v>6812</v>
+        <v>9221</v>
       </c>
     </row>
     <row r="118">
@@ -4072,22 +4072,22 @@
         <v>28306</v>
       </c>
       <c r="D118" t="n">
-        <v>22755</v>
+        <v>26548</v>
       </c>
       <c r="E118" t="n">
-        <v>5551</v>
+        <v>1758</v>
       </c>
       <c r="F118" t="n">
-        <v>19.61068324736805</v>
+        <v>6.210697378647636</v>
       </c>
       <c r="G118" t="n">
         <v>1.148456201566113</v>
       </c>
       <c r="H118" t="n">
-        <v>0.9232360936422283</v>
+        <v>1.077129062360531</v>
       </c>
       <c r="I118" t="n">
-        <v>17008</v>
+        <v>21907</v>
       </c>
     </row>
     <row r="119">
@@ -4103,22 +4103,22 @@
         <v>30790</v>
       </c>
       <c r="D119" t="n">
-        <v>26442</v>
+        <v>29061</v>
       </c>
       <c r="E119" t="n">
-        <v>4348</v>
+        <v>1729</v>
       </c>
       <c r="F119" t="n">
-        <v>14.12146800909386</v>
+        <v>5.615459564793764</v>
       </c>
       <c r="G119" t="n">
         <v>1.144056775535986</v>
       </c>
       <c r="H119" t="n">
-        <v>0.9824991639728012</v>
+        <v>1.07981272990748</v>
       </c>
       <c r="I119" t="n">
-        <v>20302</v>
+        <v>24301</v>
       </c>
     </row>
     <row r="120">
@@ -4134,22 +4134,22 @@
         <v>6873</v>
       </c>
       <c r="D120" t="n">
-        <v>6499</v>
+        <v>6666</v>
       </c>
       <c r="E120" t="n">
-        <v>374</v>
+        <v>207</v>
       </c>
       <c r="F120" t="n">
-        <v>5.441583005965372</v>
+        <v>3.011785246617197</v>
       </c>
       <c r="G120" t="n">
         <v>1.490566037735849</v>
       </c>
       <c r="H120" t="n">
-        <v>1.409455649533724</v>
+        <v>1.445673389720234</v>
       </c>
       <c r="I120" t="n">
-        <v>5558</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="121">
@@ -4165,22 +4165,22 @@
         <v>12342</v>
       </c>
       <c r="D121" t="n">
-        <v>11520</v>
+        <v>11845</v>
       </c>
       <c r="E121" t="n">
-        <v>822</v>
+        <v>497</v>
       </c>
       <c r="F121" t="n">
-        <v>6.660184735051045</v>
+        <v>4.026900016204829</v>
       </c>
       <c r="G121" t="n">
         <v>1.218601895734597</v>
       </c>
       <c r="H121" t="n">
-        <v>1.137440758293839</v>
+        <v>1.169530015797788</v>
       </c>
       <c r="I121" t="n">
-        <v>9436</v>
+        <v>10378</v>
       </c>
     </row>
     <row r="122">
@@ -4196,22 +4196,22 @@
         <v>7815</v>
       </c>
       <c r="D122" t="n">
-        <v>5962</v>
+        <v>7243</v>
       </c>
       <c r="E122" t="n">
-        <v>1853</v>
+        <v>572</v>
       </c>
       <c r="F122" t="n">
-        <v>23.7108125399872</v>
+        <v>7.319257837492002</v>
       </c>
       <c r="G122" t="n">
         <v>1.353481122272255</v>
       </c>
       <c r="H122" t="n">
-        <v>1.032559750606166</v>
+        <v>1.254416349151368</v>
       </c>
       <c r="I122" t="n">
-        <v>4115</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="123">
@@ -4227,22 +4227,22 @@
         <v>7181</v>
       </c>
       <c r="D123" t="n">
-        <v>6554</v>
+        <v>6792</v>
       </c>
       <c r="E123" t="n">
-        <v>627</v>
+        <v>389</v>
       </c>
       <c r="F123" t="n">
-        <v>8.731374460381563</v>
+        <v>5.417072831082022</v>
       </c>
       <c r="G123" t="n">
         <v>1.489524994814354</v>
       </c>
       <c r="H123" t="n">
-        <v>1.359468989836134</v>
+        <v>1.40883634100809</v>
       </c>
       <c r="I123" t="n">
-        <v>5198</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="124">
@@ -4258,22 +4258,22 @@
         <v>29783</v>
       </c>
       <c r="D124" t="n">
-        <v>25349</v>
+        <v>27373</v>
       </c>
       <c r="E124" t="n">
-        <v>4434</v>
+        <v>2410</v>
       </c>
       <c r="F124" t="n">
-        <v>14.88768760702414</v>
+        <v>8.091864486452002</v>
       </c>
       <c r="G124" t="n">
         <v>1.269901505137935</v>
       </c>
       <c r="H124" t="n">
-        <v>1.080842536136102</v>
+        <v>1.167142796230759</v>
       </c>
       <c r="I124" t="n">
-        <v>18734</v>
+        <v>21884</v>
       </c>
     </row>
     <row r="125">
@@ -4289,22 +4289,22 @@
         <v>21403</v>
       </c>
       <c r="D125" t="n">
-        <v>19013</v>
+        <v>19886</v>
       </c>
       <c r="E125" t="n">
-        <v>2390</v>
+        <v>1517</v>
       </c>
       <c r="F125" t="n">
-        <v>11.16665887959632</v>
+        <v>7.087791431107789</v>
       </c>
       <c r="G125" t="n">
         <v>1.332606936056285</v>
       </c>
       <c r="H125" t="n">
-        <v>1.18379926530104</v>
+        <v>1.23815453583214</v>
       </c>
       <c r="I125" t="n">
-        <v>14741</v>
+        <v>16145</v>
       </c>
     </row>
     <row r="126">
@@ -4320,22 +4320,22 @@
         <v>10537</v>
       </c>
       <c r="D126" t="n">
-        <v>8817</v>
+        <v>9941</v>
       </c>
       <c r="E126" t="n">
-        <v>1720</v>
+        <v>596</v>
       </c>
       <c r="F126" t="n">
-        <v>16.32343171680744</v>
+        <v>5.656258897219322</v>
       </c>
       <c r="G126" t="n">
         <v>1.464489228630994</v>
       </c>
       <c r="H126" t="n">
-        <v>1.225434329395414</v>
+        <v>1.381653926337735</v>
       </c>
       <c r="I126" t="n">
-        <v>6237</v>
+        <v>8338</v>
       </c>
     </row>
     <row r="127">
@@ -4351,22 +4351,22 @@
         <v>33196</v>
       </c>
       <c r="D127" t="n">
-        <v>29582</v>
+        <v>31646</v>
       </c>
       <c r="E127" t="n">
-        <v>3614</v>
+        <v>1550</v>
       </c>
       <c r="F127" t="n">
-        <v>10.88685383781178</v>
+        <v>4.669237257500904</v>
       </c>
       <c r="G127" t="n">
         <v>1.16743449973624</v>
       </c>
       <c r="H127" t="n">
-        <v>1.040337612097767</v>
+        <v>1.112924213117637</v>
       </c>
       <c r="I127" t="n">
-        <v>23174</v>
+        <v>27252</v>
       </c>
     </row>
     <row r="128">
@@ -4382,22 +4382,22 @@
         <v>10535</v>
       </c>
       <c r="D128" t="n">
-        <v>9307</v>
+        <v>9687</v>
       </c>
       <c r="E128" t="n">
-        <v>1228</v>
+        <v>848</v>
       </c>
       <c r="F128" t="n">
-        <v>11.65638348362601</v>
+        <v>8.049359278595158</v>
       </c>
       <c r="G128" t="n">
         <v>1.188783570300158</v>
       </c>
       <c r="H128" t="n">
-        <v>1.050214398555631</v>
+        <v>1.093094109681787</v>
       </c>
       <c r="I128" t="n">
-        <v>7518</v>
+        <v>8188</v>
       </c>
     </row>
     <row r="129">
@@ -4413,22 +4413,22 @@
         <v>13066</v>
       </c>
       <c r="D129" t="n">
-        <v>10931</v>
+        <v>12352</v>
       </c>
       <c r="E129" t="n">
-        <v>2135</v>
+        <v>714</v>
       </c>
       <c r="F129" t="n">
-        <v>16.34011939384662</v>
+        <v>5.464564518597887</v>
       </c>
       <c r="G129" t="n">
         <v>1.737962223995744</v>
       </c>
       <c r="H129" t="n">
-        <v>1.453977121574887</v>
+        <v>1.642990156956637</v>
       </c>
       <c r="I129" t="n">
-        <v>7810</v>
+        <v>10302</v>
       </c>
     </row>
     <row r="130">
@@ -4444,22 +4444,22 @@
         <v>8066</v>
       </c>
       <c r="D130" t="n">
-        <v>7058</v>
+        <v>7381</v>
       </c>
       <c r="E130" t="n">
-        <v>1008</v>
+        <v>685</v>
       </c>
       <c r="F130" t="n">
-        <v>12.49690057029507</v>
+        <v>8.49243739151996</v>
       </c>
       <c r="G130" t="n">
         <v>1.440357142857143</v>
       </c>
       <c r="H130" t="n">
-        <v>1.260357142857143</v>
+        <v>1.318035714285714</v>
       </c>
       <c r="I130" t="n">
-        <v>5420</v>
+        <v>6042</v>
       </c>
     </row>
     <row r="131">
@@ -4475,22 +4475,22 @@
         <v>7751</v>
       </c>
       <c r="D131" t="n">
-        <v>7095</v>
+        <v>7431</v>
       </c>
       <c r="E131" t="n">
-        <v>656</v>
+        <v>320</v>
       </c>
       <c r="F131" t="n">
-        <v>8.463424074312991</v>
+        <v>4.128499548445362</v>
       </c>
       <c r="G131" t="n">
         <v>1.800046446818393</v>
       </c>
       <c r="H131" t="n">
-        <v>1.647700882489549</v>
+        <v>1.725731537389689</v>
       </c>
       <c r="I131" t="n">
-        <v>5750</v>
+        <v>6539</v>
       </c>
     </row>
     <row r="132">
@@ -4506,22 +4506,22 @@
         <v>31732</v>
       </c>
       <c r="D132" t="n">
-        <v>29162</v>
+        <v>30344</v>
       </c>
       <c r="E132" t="n">
-        <v>2570</v>
+        <v>1388</v>
       </c>
       <c r="F132" t="n">
-        <v>8.099079793268626</v>
+        <v>4.374133366948191</v>
       </c>
       <c r="G132" t="n">
         <v>1.064725027681777</v>
       </c>
       <c r="H132" t="n">
-        <v>0.9784920981109284</v>
+        <v>1.0181525349797</v>
       </c>
       <c r="I132" t="n">
-        <v>23493</v>
+        <v>26360</v>
       </c>
     </row>
     <row r="133">
@@ -4537,22 +4537,22 @@
         <v>53956</v>
       </c>
       <c r="D133" t="n">
-        <v>30507</v>
+        <v>49960</v>
       </c>
       <c r="E133" t="n">
-        <v>23449</v>
+        <v>3996</v>
       </c>
       <c r="F133" t="n">
-        <v>43.45948550670917</v>
+        <v>7.406034546667656</v>
       </c>
       <c r="G133" t="n">
         <v>1.130821142641573</v>
       </c>
       <c r="H133" t="n">
-        <v>0.6393720920484554</v>
+        <v>1.047072138156516</v>
       </c>
       <c r="I133" t="n">
-        <v>19010</v>
+        <v>39123</v>
       </c>
     </row>
     <row r="134">
@@ -4568,22 +4568,22 @@
         <v>7162</v>
       </c>
       <c r="D134" t="n">
-        <v>6631</v>
+        <v>6836</v>
       </c>
       <c r="E134" t="n">
-        <v>531</v>
+        <v>326</v>
       </c>
       <c r="F134" t="n">
-        <v>7.414130131248255</v>
+        <v>4.551801172856744</v>
       </c>
       <c r="G134" t="n">
         <v>1.475180226570546</v>
       </c>
       <c r="H134" t="n">
-        <v>1.365808444902163</v>
+        <v>1.408032955715757</v>
       </c>
       <c r="I134" t="n">
-        <v>5507</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="135">
@@ -4599,22 +4599,22 @@
         <v>15356</v>
       </c>
       <c r="D135" t="n">
-        <v>13750</v>
+        <v>14610</v>
       </c>
       <c r="E135" t="n">
-        <v>1606</v>
+        <v>746</v>
       </c>
       <c r="F135" t="n">
-        <v>10.45845272206304</v>
+        <v>4.858035946861162</v>
       </c>
       <c r="G135" t="n">
         <v>1.172571777642028</v>
       </c>
       <c r="H135" t="n">
-        <v>1.049938912645082</v>
+        <v>1.115607819181429</v>
       </c>
       <c r="I135" t="n">
-        <v>11222</v>
+        <v>12881</v>
       </c>
     </row>
     <row r="136">
@@ -4630,22 +4630,22 @@
         <v>73668</v>
       </c>
       <c r="D136" t="n">
-        <v>67423</v>
+        <v>70154</v>
       </c>
       <c r="E136" t="n">
-        <v>6245</v>
+        <v>3514</v>
       </c>
       <c r="F136" t="n">
-        <v>8.477222131726123</v>
+        <v>4.770049410870392</v>
       </c>
       <c r="G136" t="n">
         <v>1.249054748300243</v>
       </c>
       <c r="H136" t="n">
-        <v>1.143169602739958</v>
+        <v>1.189474219637498</v>
       </c>
       <c r="I136" t="n">
-        <v>54153</v>
+        <v>60495</v>
       </c>
     </row>
     <row r="137">
@@ -4661,22 +4661,22 @@
         <v>13839</v>
       </c>
       <c r="D137" t="n">
-        <v>9007</v>
+        <v>12825</v>
       </c>
       <c r="E137" t="n">
-        <v>4832</v>
+        <v>1014</v>
       </c>
       <c r="F137" t="n">
-        <v>34.91581761687983</v>
+        <v>7.32711901148927</v>
       </c>
       <c r="G137" t="n">
         <v>1.296272011989509</v>
       </c>
       <c r="H137" t="n">
-        <v>0.8436680404645934</v>
+        <v>1.201292618958411</v>
       </c>
       <c r="I137" t="n">
-        <v>5838</v>
+        <v>10234</v>
       </c>
     </row>
     <row r="138">
@@ -4692,22 +4692,22 @@
         <v>41870</v>
       </c>
       <c r="D138" t="n">
-        <v>32231</v>
+        <v>39960</v>
       </c>
       <c r="E138" t="n">
-        <v>9639</v>
+        <v>1910</v>
       </c>
       <c r="F138" t="n">
-        <v>23.0212562694053</v>
+        <v>4.561738715070456</v>
       </c>
       <c r="G138" t="n">
         <v>1.030950680816487</v>
       </c>
       <c r="H138" t="n">
-        <v>0.7936128825745451</v>
+        <v>0.9839214044763992</v>
       </c>
       <c r="I138" t="n">
-        <v>22396</v>
+        <v>33415</v>
       </c>
     </row>
     <row r="139">
@@ -4723,22 +4723,22 @@
         <v>12052</v>
       </c>
       <c r="D139" t="n">
-        <v>10931</v>
+        <v>11410</v>
       </c>
       <c r="E139" t="n">
-        <v>1121</v>
+        <v>642</v>
       </c>
       <c r="F139" t="n">
-        <v>9.30136076999668</v>
+        <v>5.326916694324593</v>
       </c>
       <c r="G139" t="n">
         <v>1.252285951787199</v>
       </c>
       <c r="H139" t="n">
-        <v>1.135806317539485</v>
+        <v>1.185577722360765</v>
       </c>
       <c r="I139" t="n">
-        <v>9091</v>
+        <v>10071</v>
       </c>
     </row>
     <row r="140">
@@ -4754,22 +4754,22 @@
         <v>7929</v>
       </c>
       <c r="D140" t="n">
-        <v>7344</v>
+        <v>7591</v>
       </c>
       <c r="E140" t="n">
-        <v>585</v>
+        <v>338</v>
       </c>
       <c r="F140" t="n">
-        <v>7.377979568671964</v>
+        <v>4.262832639677135</v>
       </c>
       <c r="G140" t="n">
         <v>1.371799307958478</v>
       </c>
       <c r="H140" t="n">
-        <v>1.270588235294118</v>
+        <v>1.313321799307958</v>
       </c>
       <c r="I140" t="n">
-        <v>6081</v>
+        <v>6740</v>
       </c>
     </row>
     <row r="141">
@@ -4785,22 +4785,22 @@
         <v>12197</v>
       </c>
       <c r="D141" t="n">
-        <v>11095</v>
+        <v>11564</v>
       </c>
       <c r="E141" t="n">
-        <v>1102</v>
+        <v>633</v>
       </c>
       <c r="F141" t="n">
-        <v>9.035008608674264</v>
+        <v>5.189800770681315</v>
       </c>
       <c r="G141" t="n">
         <v>1.602548942320326</v>
       </c>
       <c r="H141" t="n">
-        <v>1.457758507423466</v>
+        <v>1.51937984496124</v>
       </c>
       <c r="I141" t="n">
-        <v>8748</v>
+        <v>9862</v>
       </c>
     </row>
     <row r="142">
@@ -4816,22 +4816,22 @@
         <v>15066</v>
       </c>
       <c r="D142" t="n">
-        <v>8871</v>
+        <v>13259</v>
       </c>
       <c r="E142" t="n">
-        <v>6195</v>
+        <v>1807</v>
       </c>
       <c r="F142" t="n">
-        <v>41.11907606531263</v>
+        <v>11.99389353511217</v>
       </c>
       <c r="G142" t="n">
         <v>1.423872979869578</v>
       </c>
       <c r="H142" t="n">
-        <v>0.8383895662035724</v>
+        <v>1.253095170588791</v>
       </c>
       <c r="I142" t="n">
-        <v>5520</v>
+        <v>9896</v>
       </c>
     </row>
     <row r="143">
@@ -4847,22 +4847,22 @@
         <v>12975</v>
       </c>
       <c r="D143" t="n">
-        <v>11433</v>
+        <v>12135</v>
       </c>
       <c r="E143" t="n">
-        <v>1542</v>
+        <v>840</v>
       </c>
       <c r="F143" t="n">
-        <v>11.88439306358381</v>
+        <v>6.473988439306358</v>
       </c>
       <c r="G143" t="n">
         <v>1.43831060857998</v>
       </c>
       <c r="H143" t="n">
-        <v>1.267376122381111</v>
+        <v>1.345194546059195</v>
       </c>
       <c r="I143" t="n">
-        <v>8690</v>
+        <v>9888</v>
       </c>
     </row>
     <row r="144">
@@ -4878,22 +4878,22 @@
         <v>14092</v>
       </c>
       <c r="D144" t="n">
-        <v>11625</v>
+        <v>13318</v>
       </c>
       <c r="E144" t="n">
-        <v>2467</v>
+        <v>774</v>
       </c>
       <c r="F144" t="n">
-        <v>17.50638660232756</v>
+        <v>5.492478001703094</v>
       </c>
       <c r="G144" t="n">
         <v>1.857632480885842</v>
       </c>
       <c r="H144" t="n">
-        <v>1.532428157131558</v>
+        <v>1.755602425520696</v>
       </c>
       <c r="I144" t="n">
-        <v>8207</v>
+        <v>11109</v>
       </c>
     </row>
     <row r="145">
@@ -4909,22 +4909,22 @@
         <v>21418</v>
       </c>
       <c r="D145" t="n">
-        <v>15963</v>
+        <v>20218</v>
       </c>
       <c r="E145" t="n">
-        <v>5455</v>
+        <v>1200</v>
       </c>
       <c r="F145" t="n">
-        <v>25.46923148753385</v>
+        <v>5.602764030254926</v>
       </c>
       <c r="G145" t="n">
         <v>1.431110517172257</v>
       </c>
       <c r="H145" t="n">
-        <v>1.066617666711212</v>
+        <v>1.350928771882935</v>
       </c>
       <c r="I145" t="n">
-        <v>10361</v>
+        <v>16160</v>
       </c>
     </row>
     <row r="146">
@@ -4940,22 +4940,22 @@
         <v>8326</v>
       </c>
       <c r="D146" t="n">
-        <v>7646</v>
+        <v>7908</v>
       </c>
       <c r="E146" t="n">
-        <v>680</v>
+        <v>418</v>
       </c>
       <c r="F146" t="n">
-        <v>8.167187124669709</v>
+        <v>5.020417967811674</v>
       </c>
       <c r="G146" t="n">
         <v>1.428620452985587</v>
       </c>
       <c r="H146" t="n">
-        <v>1.31194234728895</v>
+        <v>1.356897735072066</v>
       </c>
       <c r="I146" t="n">
-        <v>6300</v>
+        <v>6855</v>
       </c>
     </row>
     <row r="147">
@@ -4971,22 +4971,22 @@
         <v>9842</v>
       </c>
       <c r="D147" t="n">
-        <v>6550</v>
+        <v>9114</v>
       </c>
       <c r="E147" t="n">
-        <v>3292</v>
+        <v>728</v>
       </c>
       <c r="F147" t="n">
-        <v>33.44848608006502</v>
+        <v>7.396870554765292</v>
       </c>
       <c r="G147" t="n">
         <v>1.347111962770326</v>
       </c>
       <c r="H147" t="n">
-        <v>0.8965234054202026</v>
+        <v>1.247467834656447</v>
       </c>
       <c r="I147" t="n">
-        <v>4448</v>
+        <v>7532</v>
       </c>
     </row>
     <row r="148">
@@ -5002,22 +5002,22 @@
         <v>14207</v>
       </c>
       <c r="D148" t="n">
-        <v>10878</v>
+        <v>13189</v>
       </c>
       <c r="E148" t="n">
-        <v>3329</v>
+        <v>1018</v>
       </c>
       <c r="F148" t="n">
-        <v>23.43211093123108</v>
+        <v>7.16548180474414</v>
       </c>
       <c r="G148" t="n">
         <v>1.193163685227177</v>
       </c>
       <c r="H148" t="n">
-        <v>0.9135802469135802</v>
+        <v>1.107667758461409</v>
       </c>
       <c r="I148" t="n">
-        <v>7844</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="149">
@@ -5033,22 +5033,22 @@
         <v>6287</v>
       </c>
       <c r="D149" t="n">
-        <v>5594</v>
+        <v>5964</v>
       </c>
       <c r="E149" t="n">
-        <v>693</v>
+        <v>323</v>
       </c>
       <c r="F149" t="n">
-        <v>11.02274534754255</v>
+        <v>5.137585493876252</v>
       </c>
       <c r="G149" t="n">
         <v>1.291230232080509</v>
       </c>
       <c r="H149" t="n">
-        <v>1.148901211747792</v>
+        <v>1.224892174984596</v>
       </c>
       <c r="I149" t="n">
-        <v>4452</v>
+        <v>5112</v>
       </c>
     </row>
     <row r="150">
@@ -5064,22 +5064,22 @@
         <v>16130</v>
       </c>
       <c r="D150" t="n">
-        <v>13421</v>
+        <v>15155</v>
       </c>
       <c r="E150" t="n">
-        <v>2709</v>
+        <v>975</v>
       </c>
       <c r="F150" t="n">
-        <v>16.79479231246125</v>
+        <v>6.044637321760694</v>
       </c>
       <c r="G150" t="n">
         <v>1.161434331797235</v>
       </c>
       <c r="H150" t="n">
-        <v>0.9663738479262672</v>
+        <v>1.091229838709677</v>
       </c>
       <c r="I150" t="n">
-        <v>10154</v>
+        <v>12893</v>
       </c>
     </row>
     <row r="151">
@@ -5095,22 +5095,22 @@
         <v>9285</v>
       </c>
       <c r="D151" t="n">
-        <v>8123</v>
+        <v>8722</v>
       </c>
       <c r="E151" t="n">
-        <v>1162</v>
+        <v>563</v>
       </c>
       <c r="F151" t="n">
-        <v>12.51480883144857</v>
+        <v>6.063543349488422</v>
       </c>
       <c r="G151" t="n">
         <v>1.655375289712961</v>
       </c>
       <c r="H151" t="n">
-        <v>1.448208236762346</v>
+        <v>1.555000891424496</v>
       </c>
       <c r="I151" t="n">
-        <v>5915</v>
+        <v>7074</v>
       </c>
     </row>
     <row r="152">
@@ -5126,22 +5126,22 @@
         <v>22421</v>
       </c>
       <c r="D152" t="n">
-        <v>20268</v>
+        <v>21408</v>
       </c>
       <c r="E152" t="n">
-        <v>2153</v>
+        <v>1013</v>
       </c>
       <c r="F152" t="n">
-        <v>9.602604700950003</v>
+        <v>4.518085723205923</v>
       </c>
       <c r="G152" t="n">
         <v>1.229828314409522</v>
       </c>
       <c r="H152" t="n">
-        <v>1.111732762876419</v>
+        <v>1.174263616916241</v>
       </c>
       <c r="I152" t="n">
-        <v>15813</v>
+        <v>18597</v>
       </c>
     </row>
     <row r="153">
@@ -5157,22 +5157,22 @@
         <v>9622</v>
       </c>
       <c r="D153" t="n">
-        <v>8820</v>
+        <v>9152</v>
       </c>
       <c r="E153" t="n">
-        <v>802</v>
+        <v>470</v>
       </c>
       <c r="F153" t="n">
-        <v>8.335065474953232</v>
+        <v>4.884639368114737</v>
       </c>
       <c r="G153" t="n">
         <v>1.248313440581214</v>
       </c>
       <c r="H153" t="n">
-        <v>1.144265697976129</v>
+        <v>1.187337830825117</v>
       </c>
       <c r="I153" t="n">
-        <v>7126</v>
+        <v>7904</v>
       </c>
     </row>
     <row r="154">
@@ -5188,22 +5188,22 @@
         <v>11194</v>
       </c>
       <c r="D154" t="n">
-        <v>7649</v>
+        <v>10241</v>
       </c>
       <c r="E154" t="n">
-        <v>3545</v>
+        <v>953</v>
       </c>
       <c r="F154" t="n">
-        <v>31.66875111666965</v>
+        <v>8.513489369304985</v>
       </c>
       <c r="G154" t="n">
         <v>1.326303317535545</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9062796208530806</v>
+        <v>1.213388625592417</v>
       </c>
       <c r="I154" t="n">
-        <v>5062</v>
+        <v>8037</v>
       </c>
     </row>
     <row r="155">
@@ -5219,22 +5219,22 @@
         <v>44568</v>
       </c>
       <c r="D155" t="n">
-        <v>41452</v>
+        <v>42708</v>
       </c>
       <c r="E155" t="n">
-        <v>3116</v>
+        <v>1860</v>
       </c>
       <c r="F155" t="n">
-        <v>6.991563453598995</v>
+        <v>4.173397953688745</v>
       </c>
       <c r="G155" t="n">
         <v>1.207935819601041</v>
       </c>
       <c r="H155" t="n">
-        <v>1.123482220294883</v>
+        <v>1.157523850823938</v>
       </c>
       <c r="I155" t="n">
-        <v>34655</v>
+        <v>37485</v>
       </c>
     </row>
     <row r="156">
@@ -5250,22 +5250,22 @@
         <v>13796</v>
       </c>
       <c r="D156" t="n">
-        <v>12304</v>
+        <v>12792</v>
       </c>
       <c r="E156" t="n">
-        <v>1492</v>
+        <v>1004</v>
       </c>
       <c r="F156" t="n">
-        <v>10.81472890692955</v>
+        <v>7.277471730936504</v>
       </c>
       <c r="G156" t="n">
         <v>1.492912022508387</v>
       </c>
       <c r="H156" t="n">
-        <v>1.331457634455146</v>
+        <v>1.384265772102586</v>
       </c>
       <c r="I156" t="n">
-        <v>9909</v>
+        <v>10837</v>
       </c>
     </row>
     <row r="157">
@@ -5281,22 +5281,22 @@
         <v>23789</v>
       </c>
       <c r="D157" t="n">
-        <v>17903</v>
+        <v>22297</v>
       </c>
       <c r="E157" t="n">
-        <v>5886</v>
+        <v>1492</v>
       </c>
       <c r="F157" t="n">
-        <v>24.74252805918702</v>
+        <v>6.271806297028037</v>
       </c>
       <c r="G157" t="n">
         <v>1.206950786402841</v>
       </c>
       <c r="H157" t="n">
-        <v>0.9083206494165398</v>
+        <v>1.131253170979198</v>
       </c>
       <c r="I157" t="n">
-        <v>12342</v>
+        <v>18062</v>
       </c>
     </row>
     <row r="158">
@@ -5312,22 +5312,22 @@
         <v>10770</v>
       </c>
       <c r="D158" t="n">
-        <v>9593</v>
+        <v>10167</v>
       </c>
       <c r="E158" t="n">
-        <v>1177</v>
+        <v>603</v>
       </c>
       <c r="F158" t="n">
-        <v>10.92850510677809</v>
+        <v>5.598885793871866</v>
       </c>
       <c r="G158" t="n">
         <v>1.454815615291098</v>
       </c>
       <c r="H158" t="n">
-        <v>1.295826016479805</v>
+        <v>1.373362150479535</v>
       </c>
       <c r="I158" t="n">
-        <v>7329</v>
+        <v>8677</v>
       </c>
     </row>
     <row r="159">
@@ -5343,22 +5343,22 @@
         <v>6648</v>
       </c>
       <c r="D159" t="n">
-        <v>6190</v>
+        <v>6331</v>
       </c>
       <c r="E159" t="n">
-        <v>458</v>
+        <v>317</v>
       </c>
       <c r="F159" t="n">
-        <v>6.889290012033694</v>
+        <v>4.76835138387485</v>
       </c>
       <c r="G159" t="n">
         <v>1.32061978545888</v>
       </c>
       <c r="H159" t="n">
-        <v>1.22963845848232</v>
+        <v>1.257647993643226</v>
       </c>
       <c r="I159" t="n">
-        <v>5308</v>
+        <v>5678</v>
       </c>
     </row>
     <row r="160">
@@ -5374,22 +5374,22 @@
         <v>12046</v>
       </c>
       <c r="D160" t="n">
-        <v>10676</v>
+        <v>11305</v>
       </c>
       <c r="E160" t="n">
-        <v>1370</v>
+        <v>741</v>
       </c>
       <c r="F160" t="n">
-        <v>11.37306989872157</v>
+        <v>6.151419558359621</v>
       </c>
       <c r="G160" t="n">
         <v>1.348483152356431</v>
       </c>
       <c r="H160" t="n">
-        <v>1.19511922086645</v>
+        <v>1.265532295981193</v>
       </c>
       <c r="I160" t="n">
-        <v>8350</v>
+        <v>9706</v>
       </c>
     </row>
     <row r="161">
@@ -5405,22 +5405,22 @@
         <v>9055</v>
       </c>
       <c r="D161" t="n">
-        <v>8032</v>
+        <v>8407</v>
       </c>
       <c r="E161" t="n">
-        <v>1023</v>
+        <v>648</v>
       </c>
       <c r="F161" t="n">
-        <v>11.29762562120376</v>
+        <v>7.156267255659857</v>
       </c>
       <c r="G161" t="n">
         <v>1.495705318797489</v>
       </c>
       <c r="H161" t="n">
-        <v>1.326726131483317</v>
+        <v>1.388668648827222</v>
       </c>
       <c r="I161" t="n">
-        <v>6122</v>
+        <v>6902</v>
       </c>
     </row>
     <row r="162">
@@ -5436,22 +5436,22 @@
         <v>27293</v>
       </c>
       <c r="D162" t="n">
-        <v>24944</v>
+        <v>26324</v>
       </c>
       <c r="E162" t="n">
-        <v>2349</v>
+        <v>969</v>
       </c>
       <c r="F162" t="n">
-        <v>8.606602425530356</v>
+        <v>3.550360898398857</v>
       </c>
       <c r="G162" t="n">
         <v>1.123261173759157</v>
       </c>
       <c r="H162" t="n">
-        <v>1.026586550333361</v>
+        <v>1.083381348259116</v>
       </c>
       <c r="I162" t="n">
-        <v>19819</v>
+        <v>23239</v>
       </c>
     </row>
     <row r="163">
@@ -5467,22 +5467,22 @@
         <v>11716</v>
       </c>
       <c r="D163" t="n">
-        <v>10592</v>
+        <v>11136</v>
       </c>
       <c r="E163" t="n">
-        <v>1124</v>
+        <v>580</v>
       </c>
       <c r="F163" t="n">
-        <v>9.593717992488903</v>
+        <v>4.95049504950495</v>
       </c>
       <c r="G163" t="n">
         <v>2.300864100549882</v>
       </c>
       <c r="H163" t="n">
-        <v>2.08012568735271</v>
+        <v>2.186959937156324</v>
       </c>
       <c r="I163" t="n">
-        <v>8427</v>
+        <v>9621</v>
       </c>
     </row>
     <row r="164">
@@ -5498,22 +5498,22 @@
         <v>72284</v>
       </c>
       <c r="D164" t="n">
-        <v>65624</v>
+        <v>69760</v>
       </c>
       <c r="E164" t="n">
-        <v>6660</v>
+        <v>2524</v>
       </c>
       <c r="F164" t="n">
-        <v>9.213657240883183</v>
+        <v>3.491782413812186</v>
       </c>
       <c r="G164" t="n">
         <v>1.15719202753542</v>
       </c>
       <c r="H164" t="n">
-        <v>1.05057232049948</v>
+        <v>1.116785399823901</v>
       </c>
       <c r="I164" t="n">
-        <v>51245</v>
+        <v>60941</v>
       </c>
     </row>
     <row r="165">
@@ -5529,22 +5529,22 @@
         <v>9134</v>
       </c>
       <c r="D165" t="n">
-        <v>6891</v>
+        <v>8457</v>
       </c>
       <c r="E165" t="n">
-        <v>2243</v>
+        <v>677</v>
       </c>
       <c r="F165" t="n">
-        <v>24.55660170790453</v>
+        <v>7.41186774687979</v>
       </c>
       <c r="G165" t="n">
         <v>1.643396905361641</v>
       </c>
       <c r="H165" t="n">
-        <v>1.239834472831954</v>
+        <v>1.521590500179921</v>
       </c>
       <c r="I165" t="n">
-        <v>4675</v>
+        <v>6756</v>
       </c>
     </row>
     <row r="166">
@@ -5560,22 +5560,22 @@
         <v>31774</v>
       </c>
       <c r="D166" t="n">
-        <v>28419</v>
+        <v>30177</v>
       </c>
       <c r="E166" t="n">
-        <v>3355</v>
+        <v>1597</v>
       </c>
       <c r="F166" t="n">
-        <v>10.5589475671933</v>
+        <v>5.026121986529867</v>
       </c>
       <c r="G166" t="n">
         <v>1.377226821550865</v>
       </c>
       <c r="H166" t="n">
-        <v>1.231806163581986</v>
+        <v>1.30800572146851</v>
       </c>
       <c r="I166" t="n">
-        <v>21884</v>
+        <v>25763</v>
       </c>
     </row>
     <row r="167">
@@ -5591,22 +5591,22 @@
         <v>8838</v>
       </c>
       <c r="D167" t="n">
-        <v>7726</v>
+        <v>8225</v>
       </c>
       <c r="E167" t="n">
-        <v>1112</v>
+        <v>613</v>
       </c>
       <c r="F167" t="n">
-        <v>12.58203213396696</v>
+        <v>6.935958361620276</v>
       </c>
       <c r="G167" t="n">
         <v>1.302579218865144</v>
       </c>
       <c r="H167" t="n">
-        <v>1.138688282977155</v>
+        <v>1.212232866617539</v>
       </c>
       <c r="I167" t="n">
-        <v>5999</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="168">
@@ -5622,22 +5622,22 @@
         <v>7766</v>
       </c>
       <c r="D168" t="n">
-        <v>6849</v>
+        <v>7266</v>
       </c>
       <c r="E168" t="n">
-        <v>917</v>
+        <v>500</v>
       </c>
       <c r="F168" t="n">
-        <v>11.80788050476436</v>
+        <v>6.438320885912955</v>
       </c>
       <c r="G168" t="n">
         <v>1.204965089216447</v>
       </c>
       <c r="H168" t="n">
-        <v>1.062684251357642</v>
+        <v>1.127385570209465</v>
       </c>
       <c r="I168" t="n">
-        <v>5627</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="169">
@@ -5653,22 +5653,22 @@
         <v>37361</v>
       </c>
       <c r="D169" t="n">
-        <v>34541</v>
+        <v>36031</v>
       </c>
       <c r="E169" t="n">
-        <v>2820</v>
+        <v>1330</v>
       </c>
       <c r="F169" t="n">
-        <v>7.547977837852306</v>
+        <v>3.559861888065095</v>
       </c>
       <c r="G169" t="n">
         <v>1.196394261560138</v>
       </c>
       <c r="H169" t="n">
-        <v>1.106090687844242</v>
+        <v>1.153804278211861</v>
       </c>
       <c r="I169" t="n">
-        <v>27676</v>
+        <v>31534</v>
       </c>
     </row>
     <row r="170">
@@ -5684,22 +5684,22 @@
         <v>21443</v>
       </c>
       <c r="D170" t="n">
-        <v>16340</v>
+        <v>19554</v>
       </c>
       <c r="E170" t="n">
-        <v>5103</v>
+        <v>1889</v>
       </c>
       <c r="F170" t="n">
-        <v>23.79797602947349</v>
+        <v>8.809401669542508</v>
       </c>
       <c r="G170" t="n">
         <v>1.314311982837879</v>
       </c>
       <c r="H170" t="n">
-        <v>1.001532332209623</v>
+        <v>1.198528961078762</v>
       </c>
       <c r="I170" t="n">
-        <v>11274</v>
+        <v>15531</v>
       </c>
     </row>
     <row r="171">
@@ -5715,22 +5715,22 @@
         <v>36503</v>
       </c>
       <c r="D171" t="n">
-        <v>24494</v>
+        <v>34458</v>
       </c>
       <c r="E171" t="n">
-        <v>12009</v>
+        <v>2045</v>
       </c>
       <c r="F171" t="n">
-        <v>32.89866586307974</v>
+        <v>5.602279264717969</v>
       </c>
       <c r="G171" t="n">
         <v>1.22554977337586</v>
       </c>
       <c r="H171" t="n">
-        <v>0.822360248447205</v>
+        <v>1.156891052543227</v>
       </c>
       <c r="I171" t="n">
-        <v>17105</v>
+        <v>28051</v>
       </c>
     </row>
     <row r="172">
@@ -5746,22 +5746,22 @@
         <v>42557</v>
       </c>
       <c r="D172" t="n">
-        <v>35641</v>
+        <v>40440</v>
       </c>
       <c r="E172" t="n">
-        <v>6916</v>
+        <v>2117</v>
       </c>
       <c r="F172" t="n">
-        <v>16.25114552247574</v>
+        <v>4.974504781822027</v>
       </c>
       <c r="G172" t="n">
         <v>1.219747778733161</v>
       </c>
       <c r="H172" t="n">
-        <v>1.02152479220407</v>
+        <v>1.159071367153912</v>
       </c>
       <c r="I172" t="n">
-        <v>27664</v>
+        <v>34274</v>
       </c>
     </row>
     <row r="173">
@@ -5777,22 +5777,22 @@
         <v>56314</v>
       </c>
       <c r="D173" t="n">
-        <v>47072</v>
+        <v>53400</v>
       </c>
       <c r="E173" t="n">
-        <v>9242</v>
+        <v>2914</v>
       </c>
       <c r="F173" t="n">
-        <v>16.41154952587279</v>
+        <v>5.174556948538552</v>
       </c>
       <c r="G173" t="n">
         <v>1.214658556576507</v>
       </c>
       <c r="H173" t="n">
-        <v>1.015314265993702</v>
+        <v>1.151805357836159</v>
       </c>
       <c r="I173" t="n">
-        <v>35924</v>
+        <v>45269</v>
       </c>
     </row>
     <row r="174">
@@ -5808,22 +5808,22 @@
         <v>8570</v>
       </c>
       <c r="D174" t="n">
-        <v>7896</v>
+        <v>8178</v>
       </c>
       <c r="E174" t="n">
-        <v>674</v>
+        <v>392</v>
       </c>
       <c r="F174" t="n">
-        <v>7.864644107351225</v>
+        <v>4.574095682613769</v>
       </c>
       <c r="G174" t="n">
         <v>1.402389134347897</v>
       </c>
       <c r="H174" t="n">
-        <v>1.292096219931272</v>
+        <v>1.338242513500245</v>
       </c>
       <c r="I174" t="n">
-        <v>6552</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="175">
@@ -5839,22 +5839,22 @@
         <v>17044</v>
       </c>
       <c r="D175" t="n">
-        <v>11696</v>
+        <v>15709</v>
       </c>
       <c r="E175" t="n">
-        <v>5348</v>
+        <v>1335</v>
       </c>
       <c r="F175" t="n">
-        <v>31.37761088946257</v>
+        <v>7.832668387702417</v>
       </c>
       <c r="G175" t="n">
         <v>1.15795910048237</v>
       </c>
       <c r="H175" t="n">
-        <v>0.7946191996738909</v>
+        <v>1.067260004076364</v>
       </c>
       <c r="I175" t="n">
-        <v>7798</v>
+        <v>12625</v>
       </c>
     </row>
     <row r="176">
@@ -5870,22 +5870,22 @@
         <v>29757</v>
       </c>
       <c r="D176" t="n">
-        <v>22499</v>
+        <v>28327</v>
       </c>
       <c r="E176" t="n">
-        <v>7258</v>
+        <v>1430</v>
       </c>
       <c r="F176" t="n">
-        <v>24.39089962025742</v>
+        <v>4.805591961555264</v>
       </c>
       <c r="G176" t="n">
         <v>1.474724947963128</v>
       </c>
       <c r="H176" t="n">
-        <v>1.115026266230548</v>
+        <v>1.403855684408762</v>
       </c>
       <c r="I176" t="n">
-        <v>15352</v>
+        <v>23456</v>
       </c>
     </row>
     <row r="177">
@@ -5901,22 +5901,22 @@
         <v>26740</v>
       </c>
       <c r="D177" t="n">
-        <v>18264</v>
+        <v>25150</v>
       </c>
       <c r="E177" t="n">
-        <v>8476</v>
+        <v>1590</v>
       </c>
       <c r="F177" t="n">
-        <v>31.69783096484667</v>
+        <v>5.946148092744952</v>
       </c>
       <c r="G177" t="n">
         <v>1.550504464803433</v>
       </c>
       <c r="H177" t="n">
-        <v>1.05902818044764</v>
+        <v>1.458309173141598</v>
       </c>
       <c r="I177" t="n">
-        <v>11589</v>
+        <v>20035</v>
       </c>
     </row>
     <row r="178">
@@ -5932,22 +5932,22 @@
         <v>8537</v>
       </c>
       <c r="D178" t="n">
-        <v>7643</v>
+        <v>8154</v>
       </c>
       <c r="E178" t="n">
-        <v>894</v>
+        <v>383</v>
       </c>
       <c r="F178" t="n">
-        <v>10.47206278552185</v>
+        <v>4.486353519971887</v>
       </c>
       <c r="G178" t="n">
         <v>1.889134764328391</v>
       </c>
       <c r="H178" t="n">
-        <v>1.691303385704802</v>
+        <v>1.804381500331932</v>
       </c>
       <c r="I178" t="n">
-        <v>6052</v>
+        <v>7065</v>
       </c>
     </row>
     <row r="179">
@@ -5963,22 +5963,22 @@
         <v>7826</v>
       </c>
       <c r="D179" t="n">
-        <v>7222</v>
+        <v>7417</v>
       </c>
       <c r="E179" t="n">
-        <v>604</v>
+        <v>409</v>
       </c>
       <c r="F179" t="n">
-        <v>7.717863531817021</v>
+        <v>5.226169179657552</v>
       </c>
       <c r="G179" t="n">
         <v>1.460347079679045</v>
       </c>
       <c r="H179" t="n">
-        <v>1.347639484978541</v>
+        <v>1.384026870684829</v>
       </c>
       <c r="I179" t="n">
-        <v>5985</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="180">
@@ -5994,22 +5994,22 @@
         <v>31984</v>
       </c>
       <c r="D180" t="n">
-        <v>29348</v>
+        <v>30476</v>
       </c>
       <c r="E180" t="n">
-        <v>2636</v>
+        <v>1508</v>
       </c>
       <c r="F180" t="n">
-        <v>8.241620810405202</v>
+        <v>4.714857428714357</v>
       </c>
       <c r="G180" t="n">
         <v>1.153990474815991</v>
       </c>
       <c r="H180" t="n">
-        <v>1.058882955693462</v>
+        <v>1.099581469187473</v>
       </c>
       <c r="I180" t="n">
-        <v>24313</v>
+        <v>26791</v>
       </c>
     </row>
     <row r="181">
@@ -6025,22 +6025,22 @@
         <v>14366</v>
       </c>
       <c r="D181" t="n">
-        <v>9508</v>
+        <v>13082</v>
       </c>
       <c r="E181" t="n">
-        <v>4858</v>
+        <v>1284</v>
       </c>
       <c r="F181" t="n">
-        <v>33.81595433662815</v>
+        <v>8.937769734094388</v>
       </c>
       <c r="G181" t="n">
         <v>1.216735834674346</v>
       </c>
       <c r="H181" t="n">
-        <v>0.8052850004234776</v>
+        <v>1.107986787498941</v>
       </c>
       <c r="I181" t="n">
-        <v>6236</v>
+        <v>10252</v>
       </c>
     </row>
     <row r="182">
@@ -6056,22 +6056,22 @@
         <v>21742</v>
       </c>
       <c r="D182" t="n">
-        <v>19122</v>
+        <v>20719</v>
       </c>
       <c r="E182" t="n">
-        <v>2620</v>
+        <v>1023</v>
       </c>
       <c r="F182" t="n">
-        <v>12.05040934596633</v>
+        <v>4.705178916383038</v>
       </c>
       <c r="G182" t="n">
         <v>1.130100317064296</v>
       </c>
       <c r="H182" t="n">
-        <v>0.9939186028379854</v>
+        <v>1.076927075211809</v>
       </c>
       <c r="I182" t="n">
-        <v>15404</v>
+        <v>18107</v>
       </c>
     </row>
     <row r="183">
@@ -6087,22 +6087,22 @@
         <v>11452</v>
       </c>
       <c r="D183" t="n">
-        <v>10044</v>
+        <v>10829</v>
       </c>
       <c r="E183" t="n">
-        <v>1408</v>
+        <v>623</v>
       </c>
       <c r="F183" t="n">
-        <v>12.2947956688788</v>
+        <v>5.440097799511003</v>
       </c>
       <c r="G183" t="n">
         <v>1.798649285377729</v>
       </c>
       <c r="H183" t="n">
-        <v>1.577509030940788</v>
+        <v>1.700801005182975</v>
       </c>
       <c r="I183" t="n">
-        <v>7718</v>
+        <v>9187</v>
       </c>
     </row>
     <row r="184">
@@ -6118,22 +6118,22 @@
         <v>7808</v>
       </c>
       <c r="D184" t="n">
-        <v>5431</v>
+        <v>7256</v>
       </c>
       <c r="E184" t="n">
-        <v>2377</v>
+        <v>552</v>
       </c>
       <c r="F184" t="n">
-        <v>30.44313524590164</v>
+        <v>7.069672131147541</v>
       </c>
       <c r="G184" t="n">
         <v>1.390560997328584</v>
       </c>
       <c r="H184" t="n">
-        <v>0.9672306322350845</v>
+        <v>1.292252894033838</v>
       </c>
       <c r="I184" t="n">
-        <v>3491</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="185">
@@ -6149,22 +6149,22 @@
         <v>65195</v>
       </c>
       <c r="D185" t="n">
-        <v>59423</v>
+        <v>62142</v>
       </c>
       <c r="E185" t="n">
-        <v>5772</v>
+        <v>3053</v>
       </c>
       <c r="F185" t="n">
-        <v>8.853439680957129</v>
+        <v>4.682874453562389</v>
       </c>
       <c r="G185" t="n">
         <v>1.146850317518954</v>
       </c>
       <c r="H185" t="n">
-        <v>1.045314616426549</v>
+        <v>1.09314475697926</v>
       </c>
       <c r="I185" t="n">
-        <v>47562</v>
+        <v>53601</v>
       </c>
     </row>
     <row r="186">
@@ -6180,22 +6180,22 @@
         <v>52294</v>
       </c>
       <c r="D186" t="n">
-        <v>47747</v>
+        <v>49400</v>
       </c>
       <c r="E186" t="n">
-        <v>4547</v>
+        <v>2894</v>
       </c>
       <c r="F186" t="n">
-        <v>8.695070180135387</v>
+        <v>5.534095689754083</v>
       </c>
       <c r="G186" t="n">
         <v>1.257188191172228</v>
       </c>
       <c r="H186" t="n">
-        <v>1.147874795653428</v>
+        <v>1.187614193672468</v>
       </c>
       <c r="I186" t="n">
-        <v>38916</v>
+        <v>42781</v>
       </c>
     </row>
     <row r="187">
@@ -6211,22 +6211,22 @@
         <v>6784</v>
       </c>
       <c r="D187" t="n">
-        <v>6355</v>
+        <v>6497</v>
       </c>
       <c r="E187" t="n">
-        <v>429</v>
+        <v>287</v>
       </c>
       <c r="F187" t="n">
-        <v>6.32370283018868</v>
+        <v>4.230542452830189</v>
       </c>
       <c r="G187" t="n">
         <v>1.526896241278416</v>
       </c>
       <c r="H187" t="n">
-        <v>1.430339860454648</v>
+        <v>1.462300247580464</v>
       </c>
       <c r="I187" t="n">
-        <v>5362</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="188">
@@ -6242,22 +6242,22 @@
         <v>63099</v>
       </c>
       <c r="D188" t="n">
-        <v>57744</v>
+        <v>60420</v>
       </c>
       <c r="E188" t="n">
-        <v>5355</v>
+        <v>2679</v>
       </c>
       <c r="F188" t="n">
-        <v>8.48666381400656</v>
+        <v>4.245709123757904</v>
       </c>
       <c r="G188" t="n">
         <v>1.065105837075048</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9747138854191283</v>
+        <v>1.019884541372675</v>
       </c>
       <c r="I188" t="n">
-        <v>46716</v>
+        <v>53267</v>
       </c>
     </row>
     <row r="189">
@@ -6273,22 +6273,22 @@
         <v>15759</v>
       </c>
       <c r="D189" t="n">
-        <v>13354</v>
+        <v>14843</v>
       </c>
       <c r="E189" t="n">
-        <v>2405</v>
+        <v>916</v>
       </c>
       <c r="F189" t="n">
-        <v>15.26112062948157</v>
+        <v>5.812551557839964</v>
       </c>
       <c r="G189" t="n">
         <v>1.685995506579651</v>
       </c>
       <c r="H189" t="n">
-        <v>1.428693698512892</v>
+        <v>1.587996148496844</v>
       </c>
       <c r="I189" t="n">
-        <v>9704</v>
+        <v>12383</v>
       </c>
     </row>
     <row r="190">
@@ -6304,22 +6304,22 @@
         <v>8043</v>
       </c>
       <c r="D190" t="n">
-        <v>7273</v>
+        <v>7497</v>
       </c>
       <c r="E190" t="n">
-        <v>770</v>
+        <v>546</v>
       </c>
       <c r="F190" t="n">
-        <v>9.573542210617928</v>
+        <v>6.78851174934726</v>
       </c>
       <c r="G190" t="n">
         <v>1.317013263468151</v>
       </c>
       <c r="H190" t="n">
-        <v>1.190928442770591</v>
+        <v>1.227607663337154</v>
       </c>
       <c r="I190" t="n">
-        <v>6083</v>
+        <v>6641</v>
       </c>
     </row>
     <row r="191">
@@ -6335,22 +6335,22 @@
         <v>27635</v>
       </c>
       <c r="D191" t="n">
-        <v>21526</v>
+        <v>25444</v>
       </c>
       <c r="E191" t="n">
-        <v>6109</v>
+        <v>2191</v>
       </c>
       <c r="F191" t="n">
-        <v>22.10602496833726</v>
+        <v>7.928351727881309</v>
       </c>
       <c r="G191" t="n">
         <v>1.107038416856948</v>
       </c>
       <c r="H191" t="n">
-        <v>0.8623162280174659</v>
+        <v>1.019268517405761</v>
       </c>
       <c r="I191" t="n">
-        <v>14835</v>
+        <v>20780</v>
       </c>
     </row>
     <row r="192">
@@ -6366,22 +6366,22 @@
         <v>12402</v>
       </c>
       <c r="D192" t="n">
-        <v>6302</v>
+        <v>10784</v>
       </c>
       <c r="E192" t="n">
-        <v>6100</v>
+        <v>1618</v>
       </c>
       <c r="F192" t="n">
-        <v>49.18561522335107</v>
+        <v>13.04628285760361</v>
       </c>
       <c r="G192" t="n">
         <v>1.371902654867257</v>
       </c>
       <c r="H192" t="n">
-        <v>0.6971238938053097</v>
+        <v>1.192920353982301</v>
       </c>
       <c r="I192" t="n">
-        <v>3911</v>
+        <v>8126</v>
       </c>
     </row>
     <row r="193">
@@ -6397,22 +6397,22 @@
         <v>9712</v>
       </c>
       <c r="D193" t="n">
-        <v>7283</v>
+        <v>8897</v>
       </c>
       <c r="E193" t="n">
-        <v>2429</v>
+        <v>815</v>
       </c>
       <c r="F193" t="n">
-        <v>25.01029654036244</v>
+        <v>8.39168039538715</v>
       </c>
       <c r="G193" t="n">
         <v>1.625983592834422</v>
       </c>
       <c r="H193" t="n">
-        <v>1.219320274568893</v>
+        <v>1.489536246442324</v>
       </c>
       <c r="I193" t="n">
-        <v>4935</v>
+        <v>7097</v>
       </c>
     </row>
     <row r="194">
@@ -6428,22 +6428,22 @@
         <v>10547</v>
       </c>
       <c r="D194" t="n">
-        <v>8860</v>
+        <v>9884</v>
       </c>
       <c r="E194" t="n">
-        <v>1687</v>
+        <v>663</v>
       </c>
       <c r="F194" t="n">
-        <v>15.99506968806296</v>
+        <v>6.28614771973073</v>
       </c>
       <c r="G194" t="n">
         <v>1.184656857239133</v>
       </c>
       <c r="H194" t="n">
-        <v>0.9951701673593171</v>
+        <v>1.110187577221161</v>
       </c>
       <c r="I194" t="n">
-        <v>6639</v>
+        <v>8248</v>
       </c>
     </row>
     <row r="195">
@@ -6459,22 +6459,22 @@
         <v>37331</v>
       </c>
       <c r="D195" t="n">
-        <v>26190</v>
+        <v>35032</v>
       </c>
       <c r="E195" t="n">
-        <v>11141</v>
+        <v>2299</v>
       </c>
       <c r="F195" t="n">
-        <v>29.8438295250596</v>
+        <v>6.158420615574188</v>
       </c>
       <c r="G195" t="n">
         <v>1.263744075829384</v>
       </c>
       <c r="H195" t="n">
-        <v>0.8865944482058226</v>
+        <v>1.18591740013541</v>
       </c>
       <c r="I195" t="n">
-        <v>19000</v>
+        <v>28799</v>
       </c>
     </row>
     <row r="196">
@@ -6490,22 +6490,22 @@
         <v>6755</v>
       </c>
       <c r="D196" t="n">
-        <v>6338</v>
+        <v>6460</v>
       </c>
       <c r="E196" t="n">
-        <v>417</v>
+        <v>295</v>
       </c>
       <c r="F196" t="n">
-        <v>6.17320503330866</v>
+        <v>4.367135455218357</v>
       </c>
       <c r="G196" t="n">
         <v>1.381673143792187</v>
       </c>
       <c r="H196" t="n">
-        <v>1.296379627735733</v>
+        <v>1.321333606054408</v>
       </c>
       <c r="I196" t="n">
-        <v>5477</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="197">
@@ -6521,22 +6521,22 @@
         <v>13824</v>
       </c>
       <c r="D197" t="n">
-        <v>11331</v>
+        <v>12997</v>
       </c>
       <c r="E197" t="n">
-        <v>2493</v>
+        <v>827</v>
       </c>
       <c r="F197" t="n">
-        <v>18.03385416666666</v>
+        <v>5.982349537037037</v>
       </c>
       <c r="G197" t="n">
         <v>1.757437070938215</v>
       </c>
       <c r="H197" t="n">
-        <v>1.440503432494279</v>
+        <v>1.652301042461225</v>
       </c>
       <c r="I197" t="n">
-        <v>7858</v>
+        <v>10333</v>
       </c>
     </row>
     <row r="198">
@@ -6552,22 +6552,22 @@
         <v>16696</v>
       </c>
       <c r="D198" t="n">
-        <v>14112</v>
+        <v>15778</v>
       </c>
       <c r="E198" t="n">
-        <v>2584</v>
+        <v>918</v>
       </c>
       <c r="F198" t="n">
-        <v>15.47676090081456</v>
+        <v>5.498322951605175</v>
       </c>
       <c r="G198" t="n">
         <v>1.190870185449358</v>
       </c>
       <c r="H198" t="n">
-        <v>1.006562054208274</v>
+        <v>1.125392296718973</v>
       </c>
       <c r="I198" t="n">
-        <v>10982</v>
+        <v>13517</v>
       </c>
     </row>
     <row r="199">
@@ -6583,22 +6583,22 @@
         <v>16186</v>
       </c>
       <c r="D199" t="n">
-        <v>14088</v>
+        <v>15239</v>
       </c>
       <c r="E199" t="n">
-        <v>2098</v>
+        <v>947</v>
       </c>
       <c r="F199" t="n">
-        <v>12.96181885580131</v>
+        <v>5.850735203262079</v>
       </c>
       <c r="G199" t="n">
         <v>1.23679987774127</v>
       </c>
       <c r="H199" t="n">
-        <v>1.076488117979675</v>
+        <v>1.164437991900359</v>
       </c>
       <c r="I199" t="n">
-        <v>10467</v>
+        <v>12768</v>
       </c>
     </row>
     <row r="200">
@@ -6614,22 +6614,22 @@
         <v>14124</v>
       </c>
       <c r="D200" t="n">
-        <v>10171</v>
+        <v>12983</v>
       </c>
       <c r="E200" t="n">
-        <v>3953</v>
+        <v>1141</v>
       </c>
       <c r="F200" t="n">
-        <v>27.98782214670065</v>
+        <v>8.078448031719059</v>
       </c>
       <c r="G200" t="n">
         <v>1.30343300110742</v>
       </c>
       <c r="H200" t="n">
-        <v>0.9386304909560723</v>
+        <v>1.198135843484681</v>
       </c>
       <c r="I200" t="n">
-        <v>6745</v>
+        <v>10526</v>
       </c>
     </row>
   </sheetData>
